--- a/src/test/resources/excel/DBC模版.xlsx
+++ b/src/test/resources/excel/DBC模版.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_USER\SLC\Code\IDEA_Project\smartGrid\src\test\resources\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C18D69-3FBB-4581-8950-59821F45A432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA84AEA-06C9-4508-B2DD-F6B6360F3B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="21000" tabRatio="476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="476" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CanProtocol_Info" sheetId="7" r:id="rId1"/>
@@ -3252,7 +3252,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="[$¥-804]#,##0.0000000000000;[$¥-804]\-#,##0.0000000000000"/>
+    <numFmt numFmtId="176" formatCode="[$¥-804]#,##0.0000000000000;[$¥-804]\-#,##0.0000000000000"/>
   </numFmts>
   <fonts count="46" x14ac:knownFonts="1">
     <font>
@@ -3801,7 +3801,7 @@
     <xf numFmtId="0" fontId="18" fillId="9" borderId="4" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
@@ -3828,7 +3828,7 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="178" fontId="24" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="24" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
@@ -9135,21 +9135,20 @@
     <col min="14" max="14" width="11.875" style="3" customWidth="1"/>
     <col min="15" max="15" width="11.625" style="4" customWidth="1"/>
     <col min="16" max="16" width="8.875" style="4"/>
-    <col min="17" max="17" width="11.375" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="18" max="19" width="8.875" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="20" max="20" width="11" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="21" width="11.125" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="22" max="24" width="8.875" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="25" max="25" width="44.25" style="3" customWidth="1" collapsed="1"/>
-    <col min="26" max="26" width="8.25" style="3" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="27" max="27" width="8.875" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="28" max="28" width="11" style="3" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="29" max="29" width="13.75" style="3" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="30" max="30" width="11.375" style="5" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="31" max="31" width="9.75" style="5" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="32" max="32" width="8.875" style="3" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="33" max="33" width="8.875" style="3" collapsed="1"/>
-    <col min="34" max="16384" width="8.875" style="3"/>
+    <col min="17" max="17" width="11.375" style="4" customWidth="1" outlineLevel="1"/>
+    <col min="18" max="19" width="8.875" style="4" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="20" width="11" style="4" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="11.125" style="4" customWidth="1" outlineLevel="1"/>
+    <col min="22" max="24" width="8.875" style="4" customWidth="1" outlineLevel="1"/>
+    <col min="25" max="25" width="44.25" style="3" customWidth="1"/>
+    <col min="26" max="26" width="8.25" style="3" customWidth="1" outlineLevel="1"/>
+    <col min="27" max="27" width="8.875" style="4" customWidth="1" outlineLevel="1"/>
+    <col min="28" max="28" width="11" style="3" customWidth="1" outlineLevel="1"/>
+    <col min="29" max="29" width="13.75" style="3" customWidth="1" outlineLevel="1"/>
+    <col min="30" max="30" width="11.375" style="5" customWidth="1" outlineLevel="1"/>
+    <col min="31" max="31" width="9.75" style="5" customWidth="1" outlineLevel="1"/>
+    <col min="32" max="32" width="8.875" style="3" customWidth="1" outlineLevel="1"/>
+    <col min="33" max="16384" width="8.875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" s="1" customFormat="1" ht="88.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -9376,10 +9375,10 @@
       </c>
       <c r="N4" s="12"/>
       <c r="O4" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P4" s="13">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="Q4" s="13"/>
       <c r="R4" s="13"/>
@@ -9470,10 +9469,10 @@
       </c>
       <c r="N6" s="12"/>
       <c r="O6" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P6" s="13">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="Q6" s="13"/>
       <c r="R6" s="13"/>
@@ -9516,10 +9515,10 @@
       </c>
       <c r="N7" s="12"/>
       <c r="O7" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P7" s="13">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="Q7" s="13"/>
       <c r="R7" s="13"/>
@@ -9614,10 +9613,10 @@
       </c>
       <c r="N9" s="12"/>
       <c r="O9" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P9" s="13">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="Q9" s="13"/>
       <c r="R9" s="13"/>
@@ -9660,10 +9659,10 @@
       </c>
       <c r="N10" s="12"/>
       <c r="O10" s="13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P10" s="13">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="Q10" s="13"/>
       <c r="R10" s="13"/>
@@ -9983,10 +9982,10 @@
       </c>
       <c r="N4" s="12"/>
       <c r="O4" s="13">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="P4" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q4" s="13"/>
       <c r="R4" s="13"/>
@@ -10081,10 +10080,10 @@
       </c>
       <c r="N6" s="12"/>
       <c r="O6" s="13">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="P6" s="13">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q6" s="13"/>
       <c r="R6" s="13"/>
@@ -10127,10 +10126,10 @@
       </c>
       <c r="N7" s="12"/>
       <c r="O7" s="13">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="P7" s="13">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q7" s="13"/>
       <c r="R7" s="13"/>
@@ -10225,10 +10224,10 @@
       </c>
       <c r="N9" s="12"/>
       <c r="O9" s="13">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="P9" s="13">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Q9" s="13"/>
       <c r="R9" s="13"/>
@@ -10271,10 +10270,10 @@
       </c>
       <c r="N10" s="12"/>
       <c r="O10" s="13">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P10" s="13">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="Q10" s="13"/>
       <c r="R10" s="13"/>

--- a/src/test/resources/excel/DBC模版.xlsx
+++ b/src/test/resources/excel/DBC模版.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_USER\SLC\Code\IDEA_Project\smartGrid\src\test\resources\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA84AEA-06C9-4508-B2DD-F6B6360F3B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C30762E6-B2C3-4FCC-B22B-C7FA1D25D5BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="476" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="21000" tabRatio="476" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CanProtocol_Info" sheetId="7" r:id="rId1"/>
@@ -1719,6 +1719,41 @@
         </r>
       </text>
     </comment>
+    <comment ref="B11" authorId="1" shapeId="0" xr:uid="{24EEFAFB-6A0F-4942-BA1F-8B2C15165DF7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <rFont val="等线"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Normal 类型包括 Extended 和 Standard  。
+并且现程序根据id自动判断扩展帧 Extended 和标准帧 Standard ，故不必特地填写扩展帧</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="1" shapeId="0" xr:uid="{222AE9C2-F0E7-470E-81F0-83082A08FAD3}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="36"/>
+            <rFont val="Microsoft YaHei UI"/>
+            <charset val="134"/>
+          </rPr>
+          <t>注释不可以写到这里</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -2550,7 +2585,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="216">
   <si>
     <t>测试协议</t>
   </si>
@@ -2723,12 +2758,6 @@
     <t>Event</t>
   </si>
   <si>
-    <t>报文的注释可以写到这里</t>
-  </si>
-  <si>
-    <t>报文的注释也也也也可以写到这里</t>
-  </si>
-  <si>
     <t>可以在这里填写报文的备注</t>
   </si>
   <si>
@@ -2805,9 +2834,6 @@
   </si>
   <si>
     <t>Cycle</t>
-  </si>
-  <si>
-    <t>上装发给中控屏1(发给网关，网关转给中控屏)</t>
   </si>
   <si>
     <t>CabinToCCS1_FactoryID</t>
@@ -2886,9 +2912,6 @@
     <t>0x1898ffff</t>
   </si>
   <si>
-    <t>摩托罗拉格式请参照这一帧报文来编写</t>
-  </si>
-  <si>
     <t xml:space="preserve">          </t>
   </si>
   <si>
@@ -3196,9 +3219,6 @@
     <t>sig1_2</t>
   </si>
   <si>
-    <t>CCSToCabin2</t>
-  </si>
-  <si>
     <t>0x180201AB</t>
   </si>
   <si>
@@ -3244,6 +3264,16 @@
   </si>
   <si>
     <t>testProtocol</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnWriteWithRepetition</t>
+  </si>
+  <si>
+    <t>Signed</t>
+  </si>
+  <si>
+    <t>CCSToCabin2</t>
     <phoneticPr fontId="44" type="noConversion"/>
   </si>
 </sst>
@@ -3254,7 +3284,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$¥-804]#,##0.0000000000000;[$¥-804]\-#,##0.0000000000000"/>
   </numFmts>
-  <fonts count="46" x14ac:knownFonts="1">
+  <fonts count="48" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3546,6 +3576,22 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
@@ -3886,7 +3932,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4009,6 +4055,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="46" fillId="5" borderId="1" xfId="29" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="38">
     <cellStyle name="Standard_SL(Template)_PF2010_C71 CAN CMX V1.1_100817" xfId="3" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
@@ -4335,15 +4387,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="51" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B1" s="51" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="51" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
@@ -4562,12 +4614,8 @@
       <c r="F2" s="31">
         <v>8</v>
       </c>
-      <c r="G2" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="H2" s="31" t="s">
-        <v>47</v>
-      </c>
+      <c r="G2" s="32"/>
+      <c r="H2" s="31"/>
       <c r="I2" s="31"/>
       <c r="J2" s="31"/>
       <c r="K2" s="31"/>
@@ -4586,21 +4634,21 @@
       <c r="X2" s="31"/>
       <c r="Y2" s="31"/>
       <c r="Z2" s="31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA2" s="31"/>
       <c r="AB2" s="31" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AC2" s="31"/>
       <c r="AD2" s="34"/>
       <c r="AE2" s="34"/>
       <c r="AF2" s="34"/>
       <c r="AG2" s="34" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AH2" s="34" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:34" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -4611,28 +4659,28 @@
       <c r="E3" s="34"/>
       <c r="F3" s="33"/>
       <c r="G3" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="I3" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="33" t="s">
+      <c r="J3" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="I3" s="44" t="s">
+      <c r="K3" s="45">
+        <v>0</v>
+      </c>
+      <c r="L3" s="45">
+        <v>0</v>
+      </c>
+      <c r="M3" s="45">
+        <v>8</v>
+      </c>
+      <c r="N3" s="46" t="s">
         <v>54</v>
-      </c>
-      <c r="J3" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="K3" s="45">
-        <v>0</v>
-      </c>
-      <c r="L3" s="45">
-        <v>0</v>
-      </c>
-      <c r="M3" s="45">
-        <v>8</v>
-      </c>
-      <c r="N3" s="46" t="s">
-        <v>56</v>
       </c>
       <c r="O3" s="45">
         <v>1</v>
@@ -4661,14 +4709,14 @@
       <c r="W3" s="34"/>
       <c r="X3" s="34"/>
       <c r="Y3" s="33" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z3" s="33" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="AA3" s="34"/>
       <c r="AB3" s="33"/>
-      <c r="AC3" s="44"/>
+      <c r="AC3" s="52"/>
       <c r="AD3" s="33"/>
       <c r="AE3" s="33"/>
       <c r="AF3" s="33"/>
@@ -4683,16 +4731,16 @@
       <c r="E4" s="34"/>
       <c r="F4" s="33"/>
       <c r="G4" s="35" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H4" s="36" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I4" s="44" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J4" s="44" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K4" s="34">
         <v>1</v>
@@ -4704,7 +4752,7 @@
         <v>2</v>
       </c>
       <c r="N4" s="46" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O4" s="45">
         <v>1</v>
@@ -4735,14 +4783,14 @@
       </c>
       <c r="X4" s="34"/>
       <c r="Y4" s="36" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="Z4" s="33" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="AA4" s="34"/>
       <c r="AB4" s="33"/>
-      <c r="AC4" s="44"/>
+      <c r="AC4" s="52"/>
       <c r="AD4" s="33"/>
       <c r="AE4" s="33"/>
       <c r="AF4" s="33"/>
@@ -4757,16 +4805,16 @@
       <c r="E5" s="34"/>
       <c r="F5" s="33"/>
       <c r="G5" s="35" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H5" s="33" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J5" s="44" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K5" s="34">
         <v>2</v>
@@ -4778,7 +4826,7 @@
         <v>4</v>
       </c>
       <c r="N5" s="46" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O5" s="45">
         <v>1</v>
@@ -4809,14 +4857,14 @@
       </c>
       <c r="X5" s="34"/>
       <c r="Y5" s="36" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Z5" s="33" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="AA5" s="34"/>
       <c r="AB5" s="33"/>
-      <c r="AC5" s="44"/>
+      <c r="AC5" s="52"/>
       <c r="AD5" s="33"/>
       <c r="AE5" s="33"/>
       <c r="AF5" s="33"/>
@@ -4831,16 +4879,16 @@
       <c r="E6" s="34"/>
       <c r="F6" s="33"/>
       <c r="G6" s="35" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H6" s="36" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I6" s="44" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J6" s="44" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K6" s="34">
         <v>2</v>
@@ -4852,7 +4900,7 @@
         <v>4</v>
       </c>
       <c r="N6" s="46" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O6" s="45">
         <v>1</v>
@@ -4883,14 +4931,14 @@
       </c>
       <c r="X6" s="34"/>
       <c r="Y6" s="36" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Z6" s="33" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="AA6" s="34"/>
       <c r="AB6" s="33"/>
-      <c r="AC6" s="44"/>
+      <c r="AC6" s="52"/>
       <c r="AD6" s="33"/>
       <c r="AE6" s="33"/>
       <c r="AF6" s="33"/>
@@ -4905,16 +4953,16 @@
       <c r="E7" s="34"/>
       <c r="F7" s="33"/>
       <c r="G7" s="35" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H7" s="36" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I7" s="44" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J7" s="44" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K7" s="34"/>
       <c r="L7" s="34">
@@ -4924,7 +4972,7 @@
         <v>8</v>
       </c>
       <c r="N7" s="46" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O7" s="45">
         <v>1</v>
@@ -4953,16 +5001,16 @@
     </row>
     <row r="8" spans="1:34" s="24" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="37" t="s">
+      <c r="D8" s="37" t="s">
         <v>71</v>
-      </c>
-      <c r="C8" s="37" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" s="37" t="s">
-        <v>73</v>
       </c>
       <c r="E8" s="37">
         <v>100</v>
@@ -4970,12 +5018,8 @@
       <c r="F8" s="37">
         <v>8</v>
       </c>
-      <c r="G8" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="H8" s="37" t="s">
-        <v>74</v>
-      </c>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
       <c r="I8" s="37"/>
       <c r="J8" s="47"/>
       <c r="K8" s="37"/>
@@ -4996,17 +5040,17 @@
       <c r="Z8" s="37"/>
       <c r="AA8" s="37"/>
       <c r="AB8" s="37" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AC8" s="47"/>
       <c r="AD8" s="34"/>
       <c r="AE8" s="34"/>
       <c r="AF8" s="50"/>
       <c r="AG8" s="50" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AH8" s="50" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:34" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
@@ -5017,28 +5061,28 @@
       <c r="E9" s="34"/>
       <c r="F9" s="33"/>
       <c r="G9" s="33" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H9" s="33" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I9" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="J9" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="K9" s="45">
+        <v>0</v>
+      </c>
+      <c r="L9" s="45">
+        <v>0</v>
+      </c>
+      <c r="M9" s="45">
+        <v>8</v>
+      </c>
+      <c r="N9" s="46" t="s">
         <v>54</v>
-      </c>
-      <c r="J9" s="44" t="s">
-        <v>73</v>
-      </c>
-      <c r="K9" s="45">
-        <v>0</v>
-      </c>
-      <c r="L9" s="45">
-        <v>0</v>
-      </c>
-      <c r="M9" s="45">
-        <v>8</v>
-      </c>
-      <c r="N9" s="46" t="s">
-        <v>56</v>
       </c>
       <c r="O9" s="45">
         <v>1</v>
@@ -5067,12 +5111,12 @@
       <c r="W9" s="34"/>
       <c r="X9" s="34"/>
       <c r="Y9" s="33" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z9" s="33"/>
       <c r="AA9" s="34"/>
       <c r="AB9" s="33"/>
-      <c r="AC9" s="44"/>
+      <c r="AC9" s="52"/>
       <c r="AD9" s="33"/>
       <c r="AE9" s="33"/>
       <c r="AF9" s="33"/>
@@ -5087,16 +5131,16 @@
       <c r="E10" s="34"/>
       <c r="F10" s="33"/>
       <c r="G10" s="33" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H10" s="36" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I10" s="44" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J10" s="44" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K10" s="34">
         <v>1</v>
@@ -5109,7 +5153,7 @@
         <v>8</v>
       </c>
       <c r="N10" s="46" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O10" s="45">
         <v>1</v>
@@ -5156,16 +5200,16 @@
       <c r="E11" s="34"/>
       <c r="F11" s="33"/>
       <c r="G11" s="33" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H11" s="36" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I11" s="44" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J11" s="44" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K11" s="34">
         <v>2</v>
@@ -5178,7 +5222,7 @@
         <v>4</v>
       </c>
       <c r="N11" s="46" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O11" s="45">
         <v>1</v>
@@ -5207,7 +5251,7 @@
       <c r="W11" s="34"/>
       <c r="X11" s="34"/>
       <c r="Y11" s="36" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="Z11" s="36"/>
       <c r="AA11" s="34"/>
@@ -5227,16 +5271,16 @@
       <c r="E12" s="34"/>
       <c r="F12" s="33"/>
       <c r="G12" s="33" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H12" s="36" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I12" s="44" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J12" s="44" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K12" s="34">
         <v>2</v>
@@ -5248,7 +5292,7 @@
         <v>4</v>
       </c>
       <c r="N12" s="46" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O12" s="45">
         <v>1</v>
@@ -5276,10 +5320,10 @@
       </c>
       <c r="W12" s="34"/>
       <c r="X12" s="34" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="Y12" s="36" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Z12" s="36"/>
       <c r="AA12" s="34"/>
@@ -5299,16 +5343,16 @@
       <c r="E13" s="34"/>
       <c r="F13" s="33"/>
       <c r="G13" s="33" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H13" s="36" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I13" s="44" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J13" s="44" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K13" s="34">
         <v>3</v>
@@ -5320,7 +5364,7 @@
         <v>2</v>
       </c>
       <c r="N13" s="46" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O13" s="45">
         <v>1</v>
@@ -5349,7 +5393,7 @@
       <c r="W13" s="34"/>
       <c r="X13" s="34"/>
       <c r="Y13" s="36" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="Z13" s="36"/>
       <c r="AA13" s="34"/>
@@ -5369,16 +5413,16 @@
       <c r="E14" s="34"/>
       <c r="F14" s="33"/>
       <c r="G14" s="33" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H14" s="36" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I14" s="44" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J14" s="44" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K14" s="34">
         <v>3</v>
@@ -5390,7 +5434,7 @@
         <v>2</v>
       </c>
       <c r="N14" s="46" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O14" s="45">
         <v>1</v>
@@ -5419,7 +5463,7 @@
       <c r="W14" s="34"/>
       <c r="X14" s="34"/>
       <c r="Y14" s="36" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="Z14" s="36"/>
       <c r="AA14" s="34"/>
@@ -5439,16 +5483,16 @@
       <c r="E15" s="34"/>
       <c r="F15" s="33"/>
       <c r="G15" s="33" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H15" s="36" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I15" s="44" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J15" s="44" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K15" s="34">
         <v>3</v>
@@ -5460,7 +5504,7 @@
         <v>2</v>
       </c>
       <c r="N15" s="46" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O15" s="45">
         <v>1</v>
@@ -5483,7 +5527,7 @@
       <c r="W15" s="34"/>
       <c r="X15" s="34"/>
       <c r="Y15" s="36" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="Z15" s="36"/>
       <c r="AA15" s="34"/>
@@ -5503,16 +5547,16 @@
       <c r="E16" s="34"/>
       <c r="F16" s="33"/>
       <c r="G16" s="33" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H16" s="38" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I16" s="44" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J16" s="44" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K16" s="34">
         <v>7</v>
@@ -5524,7 +5568,7 @@
         <v>8</v>
       </c>
       <c r="N16" s="46" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O16" s="45">
         <v>1</v>
@@ -5553,7 +5597,7 @@
       <c r="W16" s="34"/>
       <c r="X16" s="34"/>
       <c r="Y16" s="36" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="Z16" s="36"/>
       <c r="AA16" s="34"/>
@@ -5567,16 +5611,16 @@
     </row>
     <row r="17" spans="1:34" s="25" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="39" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B17" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" s="39" t="s">
         <v>71</v>
-      </c>
-      <c r="C17" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="D17" s="39" t="s">
-        <v>73</v>
       </c>
       <c r="E17" s="39">
         <v>50</v>
@@ -5585,9 +5629,7 @@
         <v>8</v>
       </c>
       <c r="G17" s="39"/>
-      <c r="H17" s="39" t="s">
-        <v>99</v>
-      </c>
+      <c r="H17" s="39"/>
       <c r="I17" s="39"/>
       <c r="J17" s="39"/>
       <c r="K17" s="39"/>
@@ -5608,7 +5650,7 @@
       <c r="Z17" s="39"/>
       <c r="AA17" s="39"/>
       <c r="AB17" s="39" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AC17" s="39"/>
       <c r="AD17" s="34"/>
@@ -5619,7 +5661,7 @@
     </row>
     <row r="18" spans="1:34" s="26" customFormat="1" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A18" s="33" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B18" s="33"/>
       <c r="C18" s="33"/>
@@ -5627,16 +5669,16 @@
       <c r="E18" s="34"/>
       <c r="F18" s="33"/>
       <c r="G18" s="33" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H18" s="38" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="I18" s="44" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="J18" s="44" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K18" s="33"/>
       <c r="L18" s="34">
@@ -5646,7 +5688,7 @@
         <v>8</v>
       </c>
       <c r="N18" s="46" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O18" s="34">
         <v>1</v>
@@ -5675,7 +5717,7 @@
     </row>
     <row r="19" spans="1:34" s="26" customFormat="1" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A19" s="33" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B19" s="33"/>
       <c r="C19" s="33"/>
@@ -5683,14 +5725,14 @@
       <c r="E19" s="34"/>
       <c r="F19" s="33"/>
       <c r="G19" s="33" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H19" s="33"/>
       <c r="I19" s="44" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J19" s="44" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K19" s="33"/>
       <c r="L19" s="34">
@@ -5700,7 +5742,7 @@
         <v>8</v>
       </c>
       <c r="N19" s="46" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O19" s="34">
         <v>1</v>
@@ -5729,7 +5771,7 @@
     </row>
     <row r="20" spans="1:34" s="26" customFormat="1" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A20" s="33" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B20" s="33"/>
       <c r="C20" s="33"/>
@@ -5737,14 +5779,14 @@
       <c r="E20" s="34"/>
       <c r="F20" s="33"/>
       <c r="G20" s="33" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H20" s="33"/>
       <c r="I20" s="44" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="J20" s="44" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K20" s="33"/>
       <c r="L20" s="34">
@@ -5754,7 +5796,7 @@
         <v>8</v>
       </c>
       <c r="N20" s="46" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O20" s="34">
         <v>1</v>
@@ -5785,30 +5827,30 @@
       <c r="A21" s="33"/>
       <c r="B21" s="33"/>
       <c r="C21" s="33" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D21" s="33"/>
       <c r="E21" s="34"/>
       <c r="F21" s="33"/>
       <c r="G21" s="33" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H21" s="33"/>
       <c r="I21" s="44" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="J21" s="44" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K21" s="33"/>
       <c r="L21" s="48" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="M21" s="34">
         <v>4</v>
       </c>
       <c r="N21" s="46" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O21" s="34">
         <v>1</v>
@@ -5843,24 +5885,24 @@
       <c r="E22" s="34"/>
       <c r="F22" s="33"/>
       <c r="G22" s="33" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H22" s="33"/>
       <c r="I22" s="44" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="J22" s="44" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K22" s="33"/>
       <c r="L22" s="48" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="M22" s="48" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="N22" s="46" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O22" s="34">
         <v>1</v>
@@ -5895,16 +5937,16 @@
       <c r="E23" s="34"/>
       <c r="F23" s="33"/>
       <c r="G23" s="33" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H23" s="38" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I23" s="44" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="J23" s="44" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K23" s="34"/>
       <c r="L23" s="48">
@@ -5914,7 +5956,7 @@
         <v>16</v>
       </c>
       <c r="N23" s="46" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O23" s="34">
         <v>1</v>
@@ -5943,16 +5985,16 @@
     </row>
     <row r="24" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="40" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B24" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="40" t="s">
+        <v>113</v>
+      </c>
+      <c r="D24" s="40" t="s">
         <v>71</v>
-      </c>
-      <c r="C24" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="D24" s="40" t="s">
-        <v>73</v>
       </c>
       <c r="E24" s="41">
         <v>200</v>
@@ -5989,14 +6031,14 @@
       <c r="E25" s="43"/>
       <c r="F25" s="42"/>
       <c r="G25" s="42" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H25" s="42"/>
       <c r="I25" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J25" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K25" s="43"/>
       <c r="L25" s="43">
@@ -6006,7 +6048,7 @@
         <v>8</v>
       </c>
       <c r="N25" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O25" s="43">
         <v>1</v>
@@ -6033,14 +6075,14 @@
       <c r="E26" s="43"/>
       <c r="F26" s="42"/>
       <c r="G26" s="42" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H26" s="42"/>
       <c r="I26" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J26" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K26" s="43"/>
       <c r="L26" s="43">
@@ -6050,7 +6092,7 @@
         <v>8</v>
       </c>
       <c r="N26" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O26" s="43">
         <v>1</v>
@@ -6077,14 +6119,14 @@
       <c r="E27" s="43"/>
       <c r="F27" s="42"/>
       <c r="G27" s="42" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H27" s="42"/>
       <c r="I27" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J27" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K27" s="43"/>
       <c r="L27" s="43">
@@ -6094,7 +6136,7 @@
         <v>8</v>
       </c>
       <c r="N27" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O27" s="43">
         <v>1</v>
@@ -6121,14 +6163,14 @@
       <c r="E28" s="43"/>
       <c r="F28" s="42"/>
       <c r="G28" s="42" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H28" s="42"/>
       <c r="I28" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J28" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K28" s="43"/>
       <c r="L28" s="43">
@@ -6138,7 +6180,7 @@
         <v>8</v>
       </c>
       <c r="N28" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O28" s="43">
         <v>1</v>
@@ -6165,14 +6207,14 @@
       <c r="E29" s="43"/>
       <c r="F29" s="42"/>
       <c r="G29" s="42" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H29" s="42"/>
       <c r="I29" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J29" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K29" s="43"/>
       <c r="L29" s="43">
@@ -6182,7 +6224,7 @@
         <v>8</v>
       </c>
       <c r="N29" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O29" s="43">
         <v>0.2</v>
@@ -6209,14 +6251,14 @@
       <c r="E30" s="43"/>
       <c r="F30" s="42"/>
       <c r="G30" s="42" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H30" s="42"/>
       <c r="I30" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J30" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K30" s="43"/>
       <c r="L30" s="43">
@@ -6226,7 +6268,7 @@
         <v>8</v>
       </c>
       <c r="N30" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O30" s="43">
         <v>0.5</v>
@@ -6253,14 +6295,14 @@
       <c r="E31" s="43"/>
       <c r="F31" s="42"/>
       <c r="G31" s="42" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H31" s="42"/>
       <c r="I31" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J31" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K31" s="43"/>
       <c r="L31" s="43">
@@ -6270,7 +6312,7 @@
         <v>8</v>
       </c>
       <c r="N31" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O31" s="43">
         <v>0.1</v>
@@ -6297,14 +6339,14 @@
       <c r="E32" s="43"/>
       <c r="F32" s="42"/>
       <c r="G32" s="42" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H32" s="42"/>
       <c r="I32" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J32" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K32" s="43"/>
       <c r="L32" s="43">
@@ -6314,7 +6356,7 @@
         <v>8</v>
       </c>
       <c r="N32" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O32" s="43">
         <v>0.1</v>
@@ -6335,16 +6377,16 @@
     </row>
     <row r="33" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="40" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B33" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="D33" s="40" t="s">
         <v>71</v>
-      </c>
-      <c r="C33" s="40" t="s">
-        <v>127</v>
-      </c>
-      <c r="D33" s="40" t="s">
-        <v>73</v>
       </c>
       <c r="E33" s="41">
         <v>200</v>
@@ -6381,14 +6423,14 @@
       <c r="E34" s="43"/>
       <c r="F34" s="42"/>
       <c r="G34" s="42" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="H34" s="42"/>
       <c r="I34" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J34" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K34" s="43"/>
       <c r="L34" s="43">
@@ -6398,7 +6440,7 @@
         <v>8</v>
       </c>
       <c r="N34" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O34" s="43">
         <v>1</v>
@@ -6425,14 +6467,14 @@
       <c r="E35" s="43"/>
       <c r="F35" s="42"/>
       <c r="G35" s="42" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="H35" s="42"/>
       <c r="I35" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J35" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K35" s="43"/>
       <c r="L35" s="43">
@@ -6442,7 +6484,7 @@
         <v>8</v>
       </c>
       <c r="N35" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O35" s="43">
         <v>1</v>
@@ -6469,14 +6511,14 @@
       <c r="E36" s="43"/>
       <c r="F36" s="42"/>
       <c r="G36" s="42" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H36" s="42"/>
       <c r="I36" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J36" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K36" s="43"/>
       <c r="L36" s="43">
@@ -6486,7 +6528,7 @@
         <v>8</v>
       </c>
       <c r="N36" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O36" s="43">
         <v>1</v>
@@ -6513,14 +6555,14 @@
       <c r="E37" s="43"/>
       <c r="F37" s="42"/>
       <c r="G37" s="42" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H37" s="42"/>
       <c r="I37" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J37" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K37" s="43"/>
       <c r="L37" s="43">
@@ -6530,7 +6572,7 @@
         <v>8</v>
       </c>
       <c r="N37" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O37" s="43">
         <v>1</v>
@@ -6557,14 +6599,14 @@
       <c r="E38" s="43"/>
       <c r="F38" s="42"/>
       <c r="G38" s="42" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H38" s="42"/>
       <c r="I38" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J38" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K38" s="43"/>
       <c r="L38" s="43">
@@ -6574,7 +6616,7 @@
         <v>8</v>
       </c>
       <c r="N38" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O38" s="43">
         <v>1</v>
@@ -6601,14 +6643,14 @@
       <c r="E39" s="43"/>
       <c r="F39" s="42"/>
       <c r="G39" s="42" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H39" s="42"/>
       <c r="I39" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J39" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K39" s="43"/>
       <c r="L39" s="43">
@@ -6618,7 +6660,7 @@
         <v>8</v>
       </c>
       <c r="N39" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O39" s="43">
         <v>1</v>
@@ -6645,14 +6687,14 @@
       <c r="E40" s="43"/>
       <c r="F40" s="42"/>
       <c r="G40" s="42" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H40" s="42"/>
       <c r="I40" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J40" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K40" s="43"/>
       <c r="L40" s="43">
@@ -6662,7 +6704,7 @@
         <v>8</v>
       </c>
       <c r="N40" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O40" s="43">
         <v>1</v>
@@ -6689,14 +6731,14 @@
       <c r="E41" s="43"/>
       <c r="F41" s="42"/>
       <c r="G41" s="42" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H41" s="42"/>
       <c r="I41" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J41" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K41" s="43"/>
       <c r="L41" s="43">
@@ -6706,7 +6748,7 @@
         <v>8</v>
       </c>
       <c r="N41" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O41" s="43">
         <v>1</v>
@@ -6727,16 +6769,16 @@
     </row>
     <row r="42" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="40" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B42" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C42" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="D42" s="40" t="s">
         <v>71</v>
-      </c>
-      <c r="C42" s="40" t="s">
-        <v>137</v>
-      </c>
-      <c r="D42" s="40" t="s">
-        <v>73</v>
       </c>
       <c r="E42" s="41">
         <v>200</v>
@@ -6773,14 +6815,14 @@
       <c r="E43" s="43"/>
       <c r="F43" s="42"/>
       <c r="G43" s="42" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H43" s="42"/>
       <c r="I43" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J43" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K43" s="43"/>
       <c r="L43" s="43">
@@ -6790,7 +6832,7 @@
         <v>8</v>
       </c>
       <c r="N43" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O43" s="43">
         <v>1</v>
@@ -6817,14 +6859,14 @@
       <c r="E44" s="43"/>
       <c r="F44" s="42"/>
       <c r="G44" s="42" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H44" s="42"/>
       <c r="I44" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J44" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K44" s="43"/>
       <c r="L44" s="43">
@@ -6834,7 +6876,7 @@
         <v>8</v>
       </c>
       <c r="N44" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O44" s="43">
         <v>1</v>
@@ -6861,14 +6903,14 @@
       <c r="E45" s="43"/>
       <c r="F45" s="42"/>
       <c r="G45" s="42" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H45" s="42"/>
       <c r="I45" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J45" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K45" s="43"/>
       <c r="L45" s="43">
@@ -6878,7 +6920,7 @@
         <v>8</v>
       </c>
       <c r="N45" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O45" s="43">
         <v>1</v>
@@ -6905,14 +6947,14 @@
       <c r="E46" s="43"/>
       <c r="F46" s="42"/>
       <c r="G46" s="42" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="H46" s="42"/>
       <c r="I46" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J46" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K46" s="43"/>
       <c r="L46" s="43">
@@ -6922,7 +6964,7 @@
         <v>8</v>
       </c>
       <c r="N46" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O46" s="43">
         <v>1</v>
@@ -6949,14 +6991,14 @@
       <c r="E47" s="43"/>
       <c r="F47" s="42"/>
       <c r="G47" s="42" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H47" s="42"/>
       <c r="I47" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J47" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K47" s="43"/>
       <c r="L47" s="43">
@@ -6966,7 +7008,7 @@
         <v>8</v>
       </c>
       <c r="N47" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O47" s="43">
         <v>0.2</v>
@@ -6993,14 +7035,14 @@
       <c r="E48" s="43"/>
       <c r="F48" s="42"/>
       <c r="G48" s="42" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="H48" s="42"/>
       <c r="I48" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J48" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K48" s="43"/>
       <c r="L48" s="43">
@@ -7010,7 +7052,7 @@
         <v>8</v>
       </c>
       <c r="N48" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O48" s="43">
         <v>0.5</v>
@@ -7037,14 +7079,14 @@
       <c r="E49" s="43"/>
       <c r="F49" s="42"/>
       <c r="G49" s="42" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="H49" s="42"/>
       <c r="I49" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J49" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K49" s="43"/>
       <c r="L49" s="43">
@@ -7054,7 +7096,7 @@
         <v>8</v>
       </c>
       <c r="N49" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O49" s="43">
         <v>0.1</v>
@@ -7081,14 +7123,14 @@
       <c r="E50" s="43"/>
       <c r="F50" s="42"/>
       <c r="G50" s="42" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="H50" s="42"/>
       <c r="I50" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J50" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K50" s="43"/>
       <c r="L50" s="43">
@@ -7098,7 +7140,7 @@
         <v>8</v>
       </c>
       <c r="N50" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O50" s="43">
         <v>0.1</v>
@@ -7119,16 +7161,16 @@
     </row>
     <row r="51" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="40" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B51" s="39" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C51" s="40" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D51" s="40" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E51" s="41">
         <v>200</v>
@@ -7165,14 +7207,14 @@
       <c r="E52" s="43"/>
       <c r="F52" s="42"/>
       <c r="G52" s="42" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="H52" s="42"/>
       <c r="I52" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J52" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K52" s="43"/>
       <c r="L52" s="43">
@@ -7182,7 +7224,7 @@
         <v>8</v>
       </c>
       <c r="N52" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O52" s="43">
         <v>1</v>
@@ -7209,14 +7251,14 @@
       <c r="E53" s="43"/>
       <c r="F53" s="42"/>
       <c r="G53" s="42" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H53" s="42"/>
       <c r="I53" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J53" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K53" s="43"/>
       <c r="L53" s="43">
@@ -7226,7 +7268,7 @@
         <v>8</v>
       </c>
       <c r="N53" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O53" s="43">
         <v>1</v>
@@ -7253,14 +7295,14 @@
       <c r="E54" s="43"/>
       <c r="F54" s="42"/>
       <c r="G54" s="42" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H54" s="42"/>
       <c r="I54" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J54" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K54" s="43"/>
       <c r="L54" s="43">
@@ -7270,7 +7312,7 @@
         <v>8</v>
       </c>
       <c r="N54" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O54" s="43">
         <v>1</v>
@@ -7297,14 +7339,14 @@
       <c r="E55" s="43"/>
       <c r="F55" s="42"/>
       <c r="G55" s="42" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H55" s="42"/>
       <c r="I55" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J55" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K55" s="43"/>
       <c r="L55" s="43">
@@ -7314,7 +7356,7 @@
         <v>8</v>
       </c>
       <c r="N55" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O55" s="43">
         <v>1</v>
@@ -7341,14 +7383,14 @@
       <c r="E56" s="43"/>
       <c r="F56" s="42"/>
       <c r="G56" s="42" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H56" s="42"/>
       <c r="I56" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J56" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K56" s="43"/>
       <c r="L56" s="43">
@@ -7358,7 +7400,7 @@
         <v>8</v>
       </c>
       <c r="N56" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O56" s="43">
         <v>1</v>
@@ -7385,14 +7427,14 @@
       <c r="E57" s="43"/>
       <c r="F57" s="42"/>
       <c r="G57" s="42" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H57" s="42"/>
       <c r="I57" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J57" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K57" s="43"/>
       <c r="L57" s="43">
@@ -7402,7 +7444,7 @@
         <v>8</v>
       </c>
       <c r="N57" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O57" s="43">
         <v>1</v>
@@ -7429,14 +7471,14 @@
       <c r="E58" s="43"/>
       <c r="F58" s="42"/>
       <c r="G58" s="42" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H58" s="42"/>
       <c r="I58" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J58" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K58" s="43"/>
       <c r="L58" s="43">
@@ -7446,7 +7488,7 @@
         <v>8</v>
       </c>
       <c r="N58" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O58" s="43">
         <v>1</v>
@@ -7473,14 +7515,14 @@
       <c r="E59" s="43"/>
       <c r="F59" s="42"/>
       <c r="G59" s="42" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="H59" s="42"/>
       <c r="I59" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J59" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K59" s="43"/>
       <c r="L59" s="43">
@@ -7490,7 +7532,7 @@
         <v>8</v>
       </c>
       <c r="N59" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O59" s="43">
         <v>1</v>
@@ -7511,16 +7553,16 @@
     </row>
     <row r="60" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="40" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B60" s="39" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C60" s="40" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D60" s="40" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E60" s="41">
         <v>200</v>
@@ -7557,14 +7599,14 @@
       <c r="E61" s="43"/>
       <c r="F61" s="42"/>
       <c r="G61" s="42" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H61" s="42"/>
       <c r="I61" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J61" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K61" s="43"/>
       <c r="L61" s="43">
@@ -7574,7 +7616,7 @@
         <v>8</v>
       </c>
       <c r="N61" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O61" s="43">
         <v>1</v>
@@ -7601,14 +7643,14 @@
       <c r="E62" s="43"/>
       <c r="F62" s="42"/>
       <c r="G62" s="42" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="H62" s="42"/>
       <c r="I62" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J62" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K62" s="43"/>
       <c r="L62" s="43">
@@ -7618,7 +7660,7 @@
         <v>8</v>
       </c>
       <c r="N62" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O62" s="43">
         <v>1</v>
@@ -7645,14 +7687,14 @@
       <c r="E63" s="43"/>
       <c r="F63" s="42"/>
       <c r="G63" s="42" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="H63" s="42"/>
       <c r="I63" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J63" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K63" s="43"/>
       <c r="L63" s="43">
@@ -7662,7 +7704,7 @@
         <v>8</v>
       </c>
       <c r="N63" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O63" s="43">
         <v>1</v>
@@ -7689,14 +7731,14 @@
       <c r="E64" s="43"/>
       <c r="F64" s="42"/>
       <c r="G64" s="42" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H64" s="42"/>
       <c r="I64" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J64" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K64" s="43"/>
       <c r="L64" s="43">
@@ -7706,7 +7748,7 @@
         <v>8</v>
       </c>
       <c r="N64" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O64" s="43">
         <v>1</v>
@@ -7733,14 +7775,14 @@
       <c r="E65" s="43"/>
       <c r="F65" s="42"/>
       <c r="G65" s="42" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H65" s="42"/>
       <c r="I65" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J65" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K65" s="43"/>
       <c r="L65" s="43">
@@ -7750,7 +7792,7 @@
         <v>8</v>
       </c>
       <c r="N65" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O65" s="43">
         <v>0.1</v>
@@ -7777,14 +7819,14 @@
       <c r="E66" s="43"/>
       <c r="F66" s="42"/>
       <c r="G66" s="42" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="H66" s="42"/>
       <c r="I66" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J66" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K66" s="43"/>
       <c r="L66" s="43">
@@ -7794,7 +7836,7 @@
         <v>8</v>
       </c>
       <c r="N66" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O66" s="43">
         <v>0.5</v>
@@ -7821,14 +7863,14 @@
       <c r="E67" s="43"/>
       <c r="F67" s="42"/>
       <c r="G67" s="42" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H67" s="42"/>
       <c r="I67" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J67" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K67" s="43"/>
       <c r="L67" s="43">
@@ -7838,7 +7880,7 @@
         <v>8</v>
       </c>
       <c r="N67" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O67" s="43">
         <v>0.1</v>
@@ -7865,14 +7907,14 @@
       <c r="E68" s="43"/>
       <c r="F68" s="42"/>
       <c r="G68" s="42" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H68" s="42"/>
       <c r="I68" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J68" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K68" s="43"/>
       <c r="L68" s="43">
@@ -7882,7 +7924,7 @@
         <v>8</v>
       </c>
       <c r="N68" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O68" s="43">
         <v>0.1</v>
@@ -7903,16 +7945,16 @@
     </row>
     <row r="69" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="40" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B69" s="39" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C69" s="40" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D69" s="40" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E69" s="41">
         <v>200</v>
@@ -7949,14 +7991,14 @@
       <c r="E70" s="43"/>
       <c r="F70" s="42"/>
       <c r="G70" s="42" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="H70" s="42"/>
       <c r="I70" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J70" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K70" s="43"/>
       <c r="L70" s="43">
@@ -7966,7 +8008,7 @@
         <v>8</v>
       </c>
       <c r="N70" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O70" s="43">
         <v>1</v>
@@ -7993,14 +8035,14 @@
       <c r="E71" s="43"/>
       <c r="F71" s="42"/>
       <c r="G71" s="42" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H71" s="42"/>
       <c r="I71" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J71" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K71" s="43"/>
       <c r="L71" s="43">
@@ -8010,7 +8052,7 @@
         <v>8</v>
       </c>
       <c r="N71" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O71" s="43">
         <v>1</v>
@@ -8037,14 +8079,14 @@
       <c r="E72" s="43"/>
       <c r="F72" s="42"/>
       <c r="G72" s="42" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H72" s="42"/>
       <c r="I72" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J72" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K72" s="43"/>
       <c r="L72" s="43">
@@ -8054,7 +8096,7 @@
         <v>8</v>
       </c>
       <c r="N72" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O72" s="43">
         <v>1</v>
@@ -8081,14 +8123,14 @@
       <c r="E73" s="43"/>
       <c r="F73" s="42"/>
       <c r="G73" s="42" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="H73" s="42"/>
       <c r="I73" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J73" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K73" s="43"/>
       <c r="L73" s="43">
@@ -8098,7 +8140,7 @@
         <v>8</v>
       </c>
       <c r="N73" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O73" s="43">
         <v>1</v>
@@ -8125,14 +8167,14 @@
       <c r="E74" s="43"/>
       <c r="F74" s="42"/>
       <c r="G74" s="42" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H74" s="42"/>
       <c r="I74" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J74" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K74" s="43"/>
       <c r="L74" s="43">
@@ -8142,7 +8184,7 @@
         <v>8</v>
       </c>
       <c r="N74" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O74" s="43">
         <v>1</v>
@@ -8169,14 +8211,14 @@
       <c r="E75" s="43"/>
       <c r="F75" s="42"/>
       <c r="G75" s="42" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="H75" s="42"/>
       <c r="I75" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J75" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K75" s="43"/>
       <c r="L75" s="43">
@@ -8186,7 +8228,7 @@
         <v>8</v>
       </c>
       <c r="N75" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O75" s="43">
         <v>1</v>
@@ -8213,14 +8255,14 @@
       <c r="E76" s="43"/>
       <c r="F76" s="42"/>
       <c r="G76" s="42" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H76" s="42"/>
       <c r="I76" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J76" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K76" s="43"/>
       <c r="L76" s="43">
@@ -8230,7 +8272,7 @@
         <v>8</v>
       </c>
       <c r="N76" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O76" s="43">
         <v>1</v>
@@ -8257,14 +8299,14 @@
       <c r="E77" s="43"/>
       <c r="F77" s="42"/>
       <c r="G77" s="42" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="H77" s="42"/>
       <c r="I77" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J77" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K77" s="43"/>
       <c r="L77" s="43">
@@ -8274,7 +8316,7 @@
         <v>8</v>
       </c>
       <c r="N77" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O77" s="43">
         <v>1</v>
@@ -8295,16 +8337,16 @@
     </row>
     <row r="78" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="40" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B78" s="39" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C78" s="40" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D78" s="40" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E78" s="41">
         <v>200</v>
@@ -8341,14 +8383,14 @@
       <c r="E79" s="43"/>
       <c r="F79" s="42"/>
       <c r="G79" s="42" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="H79" s="42"/>
       <c r="I79" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J79" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K79" s="43"/>
       <c r="L79" s="43">
@@ -8358,7 +8400,7 @@
         <v>8</v>
       </c>
       <c r="N79" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O79" s="43">
         <v>1</v>
@@ -8385,14 +8427,14 @@
       <c r="E80" s="43"/>
       <c r="F80" s="42"/>
       <c r="G80" s="42" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="H80" s="42"/>
       <c r="I80" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J80" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K80" s="43"/>
       <c r="L80" s="43">
@@ -8402,7 +8444,7 @@
         <v>8</v>
       </c>
       <c r="N80" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O80" s="43">
         <v>1</v>
@@ -8429,14 +8471,14 @@
       <c r="E81" s="43"/>
       <c r="F81" s="42"/>
       <c r="G81" s="42" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="H81" s="42"/>
       <c r="I81" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J81" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K81" s="43"/>
       <c r="L81" s="43">
@@ -8446,7 +8488,7 @@
         <v>8</v>
       </c>
       <c r="N81" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O81" s="43">
         <v>1</v>
@@ -8473,14 +8515,14 @@
       <c r="E82" s="43"/>
       <c r="F82" s="42"/>
       <c r="G82" s="42" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="H82" s="42"/>
       <c r="I82" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J82" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K82" s="43"/>
       <c r="L82" s="43">
@@ -8490,7 +8532,7 @@
         <v>8</v>
       </c>
       <c r="N82" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O82" s="43">
         <v>1</v>
@@ -8517,14 +8559,14 @@
       <c r="E83" s="43"/>
       <c r="F83" s="42"/>
       <c r="G83" s="42" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H83" s="42"/>
       <c r="I83" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J83" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K83" s="43"/>
       <c r="L83" s="43">
@@ -8534,7 +8576,7 @@
         <v>8</v>
       </c>
       <c r="N83" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O83" s="43">
         <v>0.2</v>
@@ -8561,14 +8603,14 @@
       <c r="E84" s="43"/>
       <c r="F84" s="42"/>
       <c r="G84" s="42" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="H84" s="42"/>
       <c r="I84" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J84" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K84" s="43"/>
       <c r="L84" s="43">
@@ -8578,7 +8620,7 @@
         <v>8</v>
       </c>
       <c r="N84" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O84" s="43">
         <v>0.5</v>
@@ -8605,14 +8647,14 @@
       <c r="E85" s="43"/>
       <c r="F85" s="42"/>
       <c r="G85" s="42" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H85" s="42"/>
       <c r="I85" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J85" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K85" s="43"/>
       <c r="L85" s="43">
@@ -8622,7 +8664,7 @@
         <v>8</v>
       </c>
       <c r="N85" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O85" s="43">
         <v>0.1</v>
@@ -8649,14 +8691,14 @@
       <c r="E86" s="43"/>
       <c r="F86" s="42"/>
       <c r="G86" s="42" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H86" s="42"/>
       <c r="I86" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J86" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K86" s="43"/>
       <c r="L86" s="43">
@@ -8666,7 +8708,7 @@
         <v>8</v>
       </c>
       <c r="N86" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O86" s="43">
         <v>0.1</v>
@@ -8687,16 +8729,16 @@
     </row>
     <row r="87" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="40" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B87" s="39" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C87" s="40" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D87" s="40" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E87" s="41">
         <v>200</v>
@@ -8733,14 +8775,14 @@
       <c r="E88" s="43"/>
       <c r="F88" s="42"/>
       <c r="G88" s="42" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="H88" s="42"/>
       <c r="I88" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J88" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K88" s="43"/>
       <c r="L88" s="43">
@@ -8750,7 +8792,7 @@
         <v>8</v>
       </c>
       <c r="N88" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O88" s="43">
         <v>1</v>
@@ -8777,14 +8819,14 @@
       <c r="E89" s="43"/>
       <c r="F89" s="42"/>
       <c r="G89" s="42" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="H89" s="42"/>
       <c r="I89" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J89" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K89" s="43"/>
       <c r="L89" s="43">
@@ -8794,7 +8836,7 @@
         <v>8</v>
       </c>
       <c r="N89" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O89" s="43">
         <v>1</v>
@@ -8821,14 +8863,14 @@
       <c r="E90" s="43"/>
       <c r="F90" s="42"/>
       <c r="G90" s="42" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="H90" s="42"/>
       <c r="I90" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J90" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K90" s="43"/>
       <c r="L90" s="43">
@@ -8838,7 +8880,7 @@
         <v>8</v>
       </c>
       <c r="N90" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O90" s="43">
         <v>1</v>
@@ -8865,14 +8907,14 @@
       <c r="E91" s="43"/>
       <c r="F91" s="42"/>
       <c r="G91" s="42" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="H91" s="42"/>
       <c r="I91" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J91" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K91" s="43"/>
       <c r="L91" s="43">
@@ -8882,7 +8924,7 @@
         <v>8</v>
       </c>
       <c r="N91" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O91" s="43">
         <v>1</v>
@@ -8909,14 +8951,14 @@
       <c r="E92" s="43"/>
       <c r="F92" s="42"/>
       <c r="G92" s="42" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="H92" s="42"/>
       <c r="I92" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J92" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K92" s="43"/>
       <c r="L92" s="43">
@@ -8926,7 +8968,7 @@
         <v>8</v>
       </c>
       <c r="N92" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O92" s="43">
         <v>1</v>
@@ -8953,14 +8995,14 @@
       <c r="E93" s="43"/>
       <c r="F93" s="42"/>
       <c r="G93" s="42" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="H93" s="42"/>
       <c r="I93" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J93" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K93" s="43"/>
       <c r="L93" s="43">
@@ -8970,7 +9012,7 @@
         <v>8</v>
       </c>
       <c r="N93" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O93" s="43">
         <v>1</v>
@@ -8997,14 +9039,14 @@
       <c r="E94" s="43"/>
       <c r="F94" s="42"/>
       <c r="G94" s="42" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H94" s="42"/>
       <c r="I94" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J94" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K94" s="43"/>
       <c r="L94" s="43">
@@ -9014,7 +9056,7 @@
         <v>8</v>
       </c>
       <c r="N94" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O94" s="43">
         <v>1</v>
@@ -9041,14 +9083,14 @@
       <c r="E95" s="43"/>
       <c r="F95" s="42"/>
       <c r="G95" s="42" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H95" s="42"/>
       <c r="I95" s="42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J95" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K95" s="43"/>
       <c r="L95" s="43">
@@ -9058,7 +9100,7 @@
         <v>8</v>
       </c>
       <c r="N95" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O95" s="43">
         <v>1</v>
@@ -9117,19 +9159,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AH10"/>
+  <dimension ref="A1:AH41"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.149999999999999" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.5" style="3" customWidth="1"/>
-    <col min="2" max="2" width="10.75" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="9.875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="15.75" style="3" customWidth="1"/>
+    <col min="2" max="2" width="10.125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="17.5" style="3" customWidth="1"/>
+    <col min="4" max="4" width="9" style="3" customWidth="1"/>
     <col min="5" max="5" width="10.5" style="4" customWidth="1"/>
-    <col min="6" max="6" width="8.875" style="3"/>
-    <col min="7" max="7" width="35.75" style="3" customWidth="1"/>
-    <col min="8" max="8" width="33" style="3" customWidth="1"/>
-    <col min="9" max="9" width="8.5" style="3" customWidth="1"/>
-    <col min="10" max="10" width="9.25" style="3" customWidth="1"/>
+    <col min="6" max="6" width="2.75" style="3" customWidth="1"/>
+    <col min="7" max="7" width="19.625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="24.625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="39.25" style="3" customWidth="1"/>
+    <col min="10" max="10" width="10.875" style="3" customWidth="1"/>
     <col min="11" max="11" width="3.75" style="4" customWidth="1"/>
     <col min="12" max="13" width="8.875" style="4"/>
     <col min="14" max="14" width="11.875" style="3" customWidth="1"/>
@@ -9141,7 +9183,7 @@
     <col min="21" max="21" width="11.125" style="4" customWidth="1" outlineLevel="1"/>
     <col min="22" max="24" width="8.875" style="4" customWidth="1" outlineLevel="1"/>
     <col min="25" max="25" width="44.25" style="3" customWidth="1"/>
-    <col min="26" max="26" width="8.25" style="3" customWidth="1" outlineLevel="1"/>
+    <col min="26" max="26" width="36.625" style="3" customWidth="1" outlineLevel="1"/>
     <col min="27" max="27" width="8.875" style="4" customWidth="1" outlineLevel="1"/>
     <col min="28" max="28" width="11" style="3" customWidth="1" outlineLevel="1"/>
     <col min="29" max="29" width="13.75" style="3" customWidth="1" outlineLevel="1"/>
@@ -9252,21 +9294,21 @@
         <v>40</v>
       </c>
       <c r="AH1" s="21" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="2" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B2" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>71</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>73</v>
       </c>
       <c r="E2" s="11">
         <v>100</v>
@@ -9301,10 +9343,10 @@
       <c r="AE2" s="10"/>
       <c r="AF2" s="10"/>
       <c r="AG2" s="10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AH2" s="10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -9315,7 +9357,7 @@
       <c r="E3" s="13"/>
       <c r="F3" s="12"/>
       <c r="G3" s="12" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
@@ -9361,7 +9403,7 @@
       <c r="E4" s="13"/>
       <c r="F4" s="12"/>
       <c r="G4" s="12" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
@@ -9400,17 +9442,17 @@
       <c r="AH4" s="12"/>
     </row>
     <row r="5" spans="1:34" s="2" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>202</v>
+      <c r="A5" s="53" t="s">
+        <v>215</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>71</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>73</v>
       </c>
       <c r="E5" s="11">
         <v>100</v>
@@ -9455,7 +9497,7 @@
       <c r="E6" s="13"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
@@ -9501,7 +9543,7 @@
       <c r="E7" s="13"/>
       <c r="F7" s="12"/>
       <c r="G7" s="12" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
@@ -9541,16 +9583,16 @@
     </row>
     <row r="8" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B8" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="D8" s="15" t="s">
         <v>71</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>207</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>73</v>
       </c>
       <c r="E8" s="16">
         <v>500</v>
@@ -9585,10 +9627,10 @@
       <c r="AE8" s="15"/>
       <c r="AF8" s="15"/>
       <c r="AG8" s="15" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AH8" s="15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -9599,7 +9641,7 @@
       <c r="E9" s="13"/>
       <c r="F9" s="12"/>
       <c r="G9" s="12" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
@@ -9645,7 +9687,7 @@
       <c r="E10" s="13"/>
       <c r="F10" s="12"/>
       <c r="G10" s="12" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
@@ -9683,6 +9725,1594 @@
       <c r="AG10" s="12"/>
       <c r="AH10" s="12"/>
     </row>
+    <row r="11" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="31">
+        <v>100</v>
+      </c>
+      <c r="F11" s="31">
+        <v>8</v>
+      </c>
+      <c r="G11" s="32"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="31"/>
+      <c r="M11" s="31"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="31"/>
+      <c r="P11" s="31"/>
+      <c r="Q11" s="31"/>
+      <c r="R11" s="31"/>
+      <c r="S11" s="31"/>
+      <c r="T11" s="31"/>
+      <c r="U11" s="31"/>
+      <c r="V11" s="31"/>
+      <c r="W11" s="31"/>
+      <c r="X11" s="31"/>
+      <c r="Y11" s="31"/>
+      <c r="Z11" s="31" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="33"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="I12" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="J12" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="K12" s="45">
+        <v>0</v>
+      </c>
+      <c r="L12" s="45">
+        <v>0</v>
+      </c>
+      <c r="M12" s="45">
+        <v>8</v>
+      </c>
+      <c r="N12" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="O12" s="45">
+        <v>1</v>
+      </c>
+      <c r="P12" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="45">
+        <v>0</v>
+      </c>
+      <c r="R12" s="45">
+        <v>255</v>
+      </c>
+      <c r="S12" s="45">
+        <v>0</v>
+      </c>
+      <c r="T12" s="45">
+        <v>0</v>
+      </c>
+      <c r="U12" s="45">
+        <v>255</v>
+      </c>
+      <c r="V12" s="45">
+        <v>0</v>
+      </c>
+      <c r="W12" s="34"/>
+      <c r="X12" s="34"/>
+      <c r="Y12" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z12" s="33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="33"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="I13" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="J13" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="K13" s="34">
+        <v>1</v>
+      </c>
+      <c r="L13" s="34">
+        <v>8</v>
+      </c>
+      <c r="M13" s="34">
+        <v>2</v>
+      </c>
+      <c r="N13" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="O13" s="45">
+        <v>1</v>
+      </c>
+      <c r="P13" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="34">
+        <v>0</v>
+      </c>
+      <c r="R13" s="34">
+        <v>3</v>
+      </c>
+      <c r="S13" s="34">
+        <v>0</v>
+      </c>
+      <c r="T13" s="34">
+        <v>0</v>
+      </c>
+      <c r="U13" s="34">
+        <v>3</v>
+      </c>
+      <c r="V13" s="34">
+        <v>0</v>
+      </c>
+      <c r="W13" s="34">
+        <v>3</v>
+      </c>
+      <c r="X13" s="34"/>
+      <c r="Y13" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z13" s="33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="33"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="H14" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="I14" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="J14" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="K14" s="34">
+        <v>2</v>
+      </c>
+      <c r="L14" s="34">
+        <v>10</v>
+      </c>
+      <c r="M14" s="34">
+        <v>4</v>
+      </c>
+      <c r="N14" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="O14" s="45">
+        <v>1</v>
+      </c>
+      <c r="P14" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="34">
+        <v>0</v>
+      </c>
+      <c r="R14" s="34">
+        <v>15</v>
+      </c>
+      <c r="S14" s="34">
+        <v>0</v>
+      </c>
+      <c r="T14" s="34">
+        <v>0</v>
+      </c>
+      <c r="U14" s="34">
+        <v>15</v>
+      </c>
+      <c r="V14" s="34">
+        <v>0</v>
+      </c>
+      <c r="W14" s="34">
+        <v>15</v>
+      </c>
+      <c r="X14" s="34"/>
+      <c r="Y14" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z14" s="33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="33"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="H15" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="I15" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="J15" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="K15" s="34">
+        <v>2</v>
+      </c>
+      <c r="L15" s="34">
+        <v>14</v>
+      </c>
+      <c r="M15" s="34">
+        <v>4</v>
+      </c>
+      <c r="N15" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="O15" s="45">
+        <v>1</v>
+      </c>
+      <c r="P15" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="34">
+        <v>0</v>
+      </c>
+      <c r="R15" s="34">
+        <v>15</v>
+      </c>
+      <c r="S15" s="34">
+        <v>0</v>
+      </c>
+      <c r="T15" s="34">
+        <v>0</v>
+      </c>
+      <c r="U15" s="34">
+        <v>15</v>
+      </c>
+      <c r="V15" s="34">
+        <v>0</v>
+      </c>
+      <c r="W15" s="34">
+        <v>15</v>
+      </c>
+      <c r="X15" s="34"/>
+      <c r="Y15" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z15" s="33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="33"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="I16" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="J16" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="K16" s="34"/>
+      <c r="L16" s="34">
+        <v>56</v>
+      </c>
+      <c r="M16" s="34">
+        <v>8</v>
+      </c>
+      <c r="N16" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="O16" s="45">
+        <v>1</v>
+      </c>
+      <c r="P16" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="34"/>
+      <c r="R16" s="34"/>
+      <c r="S16" s="34"/>
+      <c r="T16" s="34"/>
+      <c r="U16" s="34"/>
+      <c r="V16" s="34"/>
+      <c r="W16" s="34"/>
+      <c r="X16" s="34"/>
+      <c r="Y16" s="36"/>
+      <c r="Z16" s="33"/>
+    </row>
+    <row r="17" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" s="37">
+        <v>100</v>
+      </c>
+      <c r="F17" s="37">
+        <v>8</v>
+      </c>
+      <c r="G17" s="37"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="37"/>
+      <c r="J17" s="47"/>
+      <c r="K17" s="37"/>
+      <c r="L17" s="37"/>
+      <c r="M17" s="37"/>
+      <c r="N17" s="37"/>
+      <c r="O17" s="37"/>
+      <c r="P17" s="37"/>
+      <c r="Q17" s="37"/>
+      <c r="R17" s="37"/>
+      <c r="S17" s="37"/>
+      <c r="T17" s="37"/>
+      <c r="U17" s="37"/>
+      <c r="V17" s="37"/>
+      <c r="W17" s="37"/>
+      <c r="X17" s="37"/>
+      <c r="Y17" s="37"/>
+      <c r="Z17" s="37"/>
+    </row>
+    <row r="18" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="33"/>
+      <c r="B18" s="33"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="I18" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="J18" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="K18" s="45">
+        <v>0</v>
+      </c>
+      <c r="L18" s="45">
+        <v>0</v>
+      </c>
+      <c r="M18" s="45">
+        <v>8</v>
+      </c>
+      <c r="N18" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="O18" s="45">
+        <v>1</v>
+      </c>
+      <c r="P18" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="45">
+        <v>0</v>
+      </c>
+      <c r="R18" s="45">
+        <v>255</v>
+      </c>
+      <c r="S18" s="45">
+        <v>0</v>
+      </c>
+      <c r="T18" s="45">
+        <v>0</v>
+      </c>
+      <c r="U18" s="45">
+        <v>255</v>
+      </c>
+      <c r="V18" s="45">
+        <v>0</v>
+      </c>
+      <c r="W18" s="34"/>
+      <c r="X18" s="34"/>
+      <c r="Y18" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z18" s="33"/>
+    </row>
+    <row r="19" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="33"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="H19" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="I19" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="J19" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="K19" s="34">
+        <v>1</v>
+      </c>
+      <c r="L19" s="34">
+        <v>8</v>
+      </c>
+      <c r="M19" s="34">
+        <v>8</v>
+      </c>
+      <c r="N19" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="O19" s="45">
+        <v>1</v>
+      </c>
+      <c r="P19" s="45">
+        <v>-50</v>
+      </c>
+      <c r="Q19" s="34">
+        <v>-50</v>
+      </c>
+      <c r="R19" s="34">
+        <v>205</v>
+      </c>
+      <c r="S19" s="34">
+        <v>20</v>
+      </c>
+      <c r="T19" s="34">
+        <v>0</v>
+      </c>
+      <c r="U19" s="34">
+        <v>255</v>
+      </c>
+      <c r="V19" s="45">
+        <v>0</v>
+      </c>
+      <c r="W19" s="34"/>
+      <c r="X19" s="34"/>
+      <c r="Y19" s="36"/>
+      <c r="Z19" s="36"/>
+    </row>
+    <row r="20" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="33"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="H20" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="I20" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="J20" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="K20" s="34">
+        <v>2</v>
+      </c>
+      <c r="L20" s="34">
+        <v>16</v>
+      </c>
+      <c r="M20" s="34">
+        <v>4</v>
+      </c>
+      <c r="N20" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="O20" s="45">
+        <v>1</v>
+      </c>
+      <c r="P20" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="34">
+        <v>0</v>
+      </c>
+      <c r="R20" s="34">
+        <v>15</v>
+      </c>
+      <c r="S20" s="34">
+        <v>0</v>
+      </c>
+      <c r="T20" s="34">
+        <v>0</v>
+      </c>
+      <c r="U20" s="34">
+        <v>15</v>
+      </c>
+      <c r="V20" s="45">
+        <v>0</v>
+      </c>
+      <c r="W20" s="34"/>
+      <c r="X20" s="34"/>
+      <c r="Y20" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z20" s="36"/>
+    </row>
+    <row r="21" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="33"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="H21" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="I21" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="J21" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="K21" s="34">
+        <v>2</v>
+      </c>
+      <c r="L21" s="34">
+        <v>20</v>
+      </c>
+      <c r="M21" s="34">
+        <v>4</v>
+      </c>
+      <c r="N21" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="O21" s="45">
+        <v>1</v>
+      </c>
+      <c r="P21" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="34">
+        <v>0</v>
+      </c>
+      <c r="R21" s="34">
+        <v>15</v>
+      </c>
+      <c r="S21" s="34">
+        <v>0</v>
+      </c>
+      <c r="T21" s="34">
+        <v>0</v>
+      </c>
+      <c r="U21" s="34">
+        <v>15</v>
+      </c>
+      <c r="V21" s="45">
+        <v>0</v>
+      </c>
+      <c r="W21" s="34"/>
+      <c r="X21" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y21" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z21" s="36"/>
+    </row>
+    <row r="22" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="33"/>
+      <c r="B22" s="33"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="H22" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="I22" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="J22" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="K22" s="34">
+        <v>3</v>
+      </c>
+      <c r="L22" s="34">
+        <v>24</v>
+      </c>
+      <c r="M22" s="34">
+        <v>2</v>
+      </c>
+      <c r="N22" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="O22" s="45">
+        <v>1</v>
+      </c>
+      <c r="P22" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="34">
+        <v>0</v>
+      </c>
+      <c r="R22" s="34">
+        <v>3</v>
+      </c>
+      <c r="S22" s="34">
+        <v>0</v>
+      </c>
+      <c r="T22" s="34">
+        <v>0</v>
+      </c>
+      <c r="U22" s="34">
+        <v>3</v>
+      </c>
+      <c r="V22" s="45">
+        <v>0</v>
+      </c>
+      <c r="W22" s="34"/>
+      <c r="X22" s="34"/>
+      <c r="Y22" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z22" s="36"/>
+    </row>
+    <row r="23" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="33"/>
+      <c r="B23" s="33"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="H23" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="I23" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="J23" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="K23" s="34">
+        <v>3</v>
+      </c>
+      <c r="L23" s="34">
+        <v>26</v>
+      </c>
+      <c r="M23" s="34">
+        <v>2</v>
+      </c>
+      <c r="N23" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="O23" s="45">
+        <v>1</v>
+      </c>
+      <c r="P23" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="34">
+        <v>0</v>
+      </c>
+      <c r="R23" s="34">
+        <v>3</v>
+      </c>
+      <c r="S23" s="34">
+        <v>0</v>
+      </c>
+      <c r="T23" s="34">
+        <v>0</v>
+      </c>
+      <c r="U23" s="34">
+        <v>3</v>
+      </c>
+      <c r="V23" s="45">
+        <v>0</v>
+      </c>
+      <c r="W23" s="34"/>
+      <c r="X23" s="34"/>
+      <c r="Y23" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z23" s="36"/>
+    </row>
+    <row r="24" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="33"/>
+      <c r="B24" s="33"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="H24" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="I24" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="J24" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="K24" s="34">
+        <v>3</v>
+      </c>
+      <c r="L24" s="34">
+        <v>28</v>
+      </c>
+      <c r="M24" s="34">
+        <v>2</v>
+      </c>
+      <c r="N24" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="O24" s="45">
+        <v>1</v>
+      </c>
+      <c r="P24" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="34">
+        <v>0</v>
+      </c>
+      <c r="R24" s="34">
+        <v>3</v>
+      </c>
+      <c r="S24" s="34">
+        <v>0</v>
+      </c>
+      <c r="T24" s="34"/>
+      <c r="U24" s="34"/>
+      <c r="V24" s="45"/>
+      <c r="W24" s="34"/>
+      <c r="X24" s="34"/>
+      <c r="Y24" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z24" s="36"/>
+    </row>
+    <row r="25" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="33"/>
+      <c r="B25" s="33"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="H25" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="I25" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="J25" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="K25" s="34">
+        <v>7</v>
+      </c>
+      <c r="L25" s="34">
+        <v>56</v>
+      </c>
+      <c r="M25" s="34">
+        <v>8</v>
+      </c>
+      <c r="N25" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="O25" s="45">
+        <v>1</v>
+      </c>
+      <c r="P25" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="34">
+        <v>0</v>
+      </c>
+      <c r="R25" s="34">
+        <v>255</v>
+      </c>
+      <c r="S25" s="34">
+        <v>0</v>
+      </c>
+      <c r="T25" s="34">
+        <v>0</v>
+      </c>
+      <c r="U25" s="34">
+        <v>255</v>
+      </c>
+      <c r="V25" s="45">
+        <v>0</v>
+      </c>
+      <c r="W25" s="34"/>
+      <c r="X25" s="34"/>
+      <c r="Y25" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z25" s="36"/>
+    </row>
+    <row r="26" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="D26" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="E26" s="39">
+        <v>50</v>
+      </c>
+      <c r="F26" s="39">
+        <v>8</v>
+      </c>
+      <c r="G26" s="39"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="39"/>
+      <c r="K26" s="39"/>
+      <c r="L26" s="39"/>
+      <c r="M26" s="39"/>
+      <c r="N26" s="39"/>
+      <c r="O26" s="39"/>
+      <c r="P26" s="39"/>
+      <c r="Q26" s="39"/>
+      <c r="R26" s="39"/>
+      <c r="S26" s="39"/>
+      <c r="T26" s="39"/>
+      <c r="U26" s="39"/>
+      <c r="V26" s="39"/>
+      <c r="W26" s="39"/>
+      <c r="X26" s="39"/>
+      <c r="Y26" s="39"/>
+      <c r="Z26" s="39"/>
+    </row>
+    <row r="27" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27" s="33"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="H27" s="38" t="s">
+        <v>98</v>
+      </c>
+      <c r="I27" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="J27" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="K27" s="33"/>
+      <c r="L27" s="34">
+        <v>7</v>
+      </c>
+      <c r="M27" s="34">
+        <v>8</v>
+      </c>
+      <c r="N27" s="46" t="s">
+        <v>214</v>
+      </c>
+      <c r="O27" s="34">
+        <v>1</v>
+      </c>
+      <c r="P27" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="33"/>
+      <c r="R27" s="33"/>
+      <c r="S27" s="33"/>
+      <c r="T27" s="33"/>
+      <c r="U27" s="33"/>
+      <c r="V27" s="33"/>
+      <c r="W27" s="33"/>
+      <c r="X27" s="33"/>
+      <c r="Y27" s="33"/>
+      <c r="Z27" s="33"/>
+    </row>
+    <row r="28" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B28" s="33"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="H28" s="33"/>
+      <c r="I28" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="J28" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="K28" s="33"/>
+      <c r="L28" s="34">
+        <v>8</v>
+      </c>
+      <c r="M28" s="34">
+        <v>8</v>
+      </c>
+      <c r="N28" s="46" t="s">
+        <v>214</v>
+      </c>
+      <c r="O28" s="34">
+        <v>1</v>
+      </c>
+      <c r="P28" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="33"/>
+      <c r="R28" s="33"/>
+      <c r="S28" s="33"/>
+      <c r="T28" s="33"/>
+      <c r="U28" s="33"/>
+      <c r="V28" s="33"/>
+      <c r="W28" s="33"/>
+      <c r="X28" s="33"/>
+      <c r="Y28" s="33"/>
+      <c r="Z28" s="33"/>
+    </row>
+    <row r="29" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="B29" s="33"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="H29" s="33"/>
+      <c r="I29" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="J29" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="K29" s="33"/>
+      <c r="L29" s="34">
+        <v>20</v>
+      </c>
+      <c r="M29" s="34">
+        <v>8</v>
+      </c>
+      <c r="N29" s="46" t="s">
+        <v>214</v>
+      </c>
+      <c r="O29" s="34">
+        <v>1</v>
+      </c>
+      <c r="P29" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="33"/>
+      <c r="R29" s="33"/>
+      <c r="S29" s="33"/>
+      <c r="T29" s="33"/>
+      <c r="U29" s="33"/>
+      <c r="V29" s="33"/>
+      <c r="W29" s="33"/>
+      <c r="X29" s="33"/>
+      <c r="Y29" s="33"/>
+      <c r="Z29" s="33"/>
+    </row>
+    <row r="30" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="33"/>
+      <c r="B30" s="33"/>
+      <c r="C30" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="D30" s="33"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="H30" s="33"/>
+      <c r="I30" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="J30" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="K30" s="33"/>
+      <c r="L30" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="M30" s="34">
+        <v>4</v>
+      </c>
+      <c r="N30" s="46" t="s">
+        <v>214</v>
+      </c>
+      <c r="O30" s="34">
+        <v>1</v>
+      </c>
+      <c r="P30" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="33"/>
+      <c r="R30" s="33"/>
+      <c r="S30" s="33"/>
+      <c r="T30" s="33"/>
+      <c r="U30" s="33"/>
+      <c r="V30" s="33"/>
+      <c r="W30" s="33"/>
+      <c r="X30" s="33"/>
+      <c r="Y30" s="33"/>
+      <c r="Z30" s="33"/>
+    </row>
+    <row r="31" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="33"/>
+      <c r="B31" s="33"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="H31" s="33"/>
+      <c r="I31" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="J31" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="K31" s="33"/>
+      <c r="L31" s="48" t="s">
+        <v>108</v>
+      </c>
+      <c r="M31" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="N31" s="46" t="s">
+        <v>214</v>
+      </c>
+      <c r="O31" s="34">
+        <v>1</v>
+      </c>
+      <c r="P31" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="33"/>
+      <c r="R31" s="33"/>
+      <c r="S31" s="33"/>
+      <c r="T31" s="33"/>
+      <c r="U31" s="33"/>
+      <c r="V31" s="33"/>
+      <c r="W31" s="33"/>
+      <c r="X31" s="33"/>
+      <c r="Y31" s="33"/>
+      <c r="Z31" s="33"/>
+    </row>
+    <row r="32" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="33"/>
+      <c r="B32" s="33"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="33" t="s">
+        <v>110</v>
+      </c>
+      <c r="H32" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="I32" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="J32" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="K32" s="34"/>
+      <c r="L32" s="48">
+        <v>41</v>
+      </c>
+      <c r="M32" s="48">
+        <v>16</v>
+      </c>
+      <c r="N32" s="46" t="s">
+        <v>214</v>
+      </c>
+      <c r="O32" s="34">
+        <v>1</v>
+      </c>
+      <c r="P32" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="34"/>
+      <c r="R32" s="34"/>
+      <c r="S32" s="34"/>
+      <c r="T32" s="34"/>
+      <c r="U32" s="34"/>
+      <c r="V32" s="34"/>
+      <c r="W32" s="34"/>
+      <c r="X32" s="34"/>
+      <c r="Y32" s="33"/>
+      <c r="Z32" s="33"/>
+    </row>
+    <row r="33" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="40" t="s">
+        <v>112</v>
+      </c>
+      <c r="B33" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="40" t="s">
+        <v>113</v>
+      </c>
+      <c r="D33" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="E33" s="41">
+        <v>200</v>
+      </c>
+      <c r="F33" s="40">
+        <v>8</v>
+      </c>
+      <c r="G33" s="40"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="40"/>
+      <c r="J33" s="40"/>
+      <c r="K33" s="41"/>
+      <c r="L33" s="41"/>
+      <c r="M33" s="41"/>
+      <c r="N33" s="40"/>
+      <c r="O33" s="41"/>
+      <c r="P33" s="41"/>
+      <c r="Q33" s="41"/>
+      <c r="R33" s="41"/>
+      <c r="S33" s="41"/>
+      <c r="T33" s="41"/>
+      <c r="U33" s="41"/>
+      <c r="V33" s="41"/>
+      <c r="W33" s="41"/>
+      <c r="X33" s="41"/>
+      <c r="Y33" s="40"/>
+      <c r="Z33" s="40"/>
+    </row>
+    <row r="34" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="42"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="H34" s="42"/>
+      <c r="I34" s="42" t="s">
+        <v>52</v>
+      </c>
+      <c r="J34" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="K34" s="43"/>
+      <c r="L34" s="43">
+        <v>0</v>
+      </c>
+      <c r="M34" s="43">
+        <v>8</v>
+      </c>
+      <c r="N34" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="O34" s="43">
+        <v>1</v>
+      </c>
+      <c r="P34" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="43"/>
+      <c r="R34" s="43"/>
+      <c r="S34" s="43"/>
+      <c r="T34" s="43"/>
+      <c r="U34" s="43"/>
+      <c r="V34" s="43"/>
+      <c r="W34" s="43"/>
+      <c r="X34" s="43"/>
+      <c r="Y34" s="42"/>
+      <c r="Z34" s="42"/>
+    </row>
+    <row r="35" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="42"/>
+      <c r="B35" s="42"/>
+      <c r="C35" s="42"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="42"/>
+      <c r="G35" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="H35" s="42"/>
+      <c r="I35" s="42" t="s">
+        <v>52</v>
+      </c>
+      <c r="J35" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="K35" s="43"/>
+      <c r="L35" s="43">
+        <v>8</v>
+      </c>
+      <c r="M35" s="43">
+        <v>8</v>
+      </c>
+      <c r="N35" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="O35" s="43">
+        <v>1</v>
+      </c>
+      <c r="P35" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="43"/>
+      <c r="R35" s="43"/>
+      <c r="S35" s="43"/>
+      <c r="T35" s="43"/>
+      <c r="U35" s="43"/>
+      <c r="V35" s="43"/>
+      <c r="W35" s="43"/>
+      <c r="X35" s="43"/>
+      <c r="Y35" s="42"/>
+      <c r="Z35" s="42"/>
+    </row>
+    <row r="36" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="42"/>
+      <c r="B36" s="42"/>
+      <c r="C36" s="42"/>
+      <c r="D36" s="42"/>
+      <c r="E36" s="43"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="42" t="s">
+        <v>116</v>
+      </c>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42" t="s">
+        <v>52</v>
+      </c>
+      <c r="J36" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="K36" s="43"/>
+      <c r="L36" s="43">
+        <v>16</v>
+      </c>
+      <c r="M36" s="43">
+        <v>8</v>
+      </c>
+      <c r="N36" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="O36" s="43">
+        <v>1</v>
+      </c>
+      <c r="P36" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="43"/>
+      <c r="R36" s="43"/>
+      <c r="S36" s="43"/>
+      <c r="T36" s="43"/>
+      <c r="U36" s="43"/>
+      <c r="V36" s="43"/>
+      <c r="W36" s="43"/>
+      <c r="X36" s="43"/>
+      <c r="Y36" s="42"/>
+      <c r="Z36" s="42"/>
+    </row>
+    <row r="37" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="42"/>
+      <c r="B37" s="42"/>
+      <c r="C37" s="42"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="42"/>
+      <c r="G37" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="H37" s="42"/>
+      <c r="I37" s="42" t="s">
+        <v>52</v>
+      </c>
+      <c r="J37" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="K37" s="43"/>
+      <c r="L37" s="43">
+        <v>24</v>
+      </c>
+      <c r="M37" s="43">
+        <v>8</v>
+      </c>
+      <c r="N37" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="O37" s="43">
+        <v>1</v>
+      </c>
+      <c r="P37" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="43"/>
+      <c r="R37" s="43"/>
+      <c r="S37" s="43"/>
+      <c r="T37" s="43"/>
+      <c r="U37" s="43"/>
+      <c r="V37" s="43"/>
+      <c r="W37" s="43"/>
+      <c r="X37" s="43"/>
+      <c r="Y37" s="42"/>
+      <c r="Z37" s="42"/>
+    </row>
+    <row r="38" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="42"/>
+      <c r="B38" s="42"/>
+      <c r="C38" s="42"/>
+      <c r="D38" s="42"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="42"/>
+      <c r="G38" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="H38" s="42"/>
+      <c r="I38" s="42" t="s">
+        <v>52</v>
+      </c>
+      <c r="J38" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="K38" s="43"/>
+      <c r="L38" s="43">
+        <v>32</v>
+      </c>
+      <c r="M38" s="43">
+        <v>8</v>
+      </c>
+      <c r="N38" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="O38" s="43">
+        <v>0.2</v>
+      </c>
+      <c r="P38" s="43">
+        <v>-20</v>
+      </c>
+      <c r="Q38" s="43"/>
+      <c r="R38" s="43"/>
+      <c r="S38" s="43"/>
+      <c r="T38" s="43"/>
+      <c r="U38" s="43"/>
+      <c r="V38" s="43"/>
+      <c r="W38" s="43"/>
+      <c r="X38" s="43"/>
+      <c r="Y38" s="42"/>
+      <c r="Z38" s="42"/>
+    </row>
+    <row r="39" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="42"/>
+      <c r="B39" s="42"/>
+      <c r="C39" s="42"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="42"/>
+      <c r="G39" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="H39" s="42"/>
+      <c r="I39" s="42" t="s">
+        <v>52</v>
+      </c>
+      <c r="J39" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="K39" s="43"/>
+      <c r="L39" s="43">
+        <v>40</v>
+      </c>
+      <c r="M39" s="43">
+        <v>8</v>
+      </c>
+      <c r="N39" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="O39" s="43">
+        <v>0.5</v>
+      </c>
+      <c r="P39" s="43">
+        <v>-50</v>
+      </c>
+      <c r="Q39" s="43"/>
+      <c r="R39" s="43"/>
+      <c r="S39" s="43"/>
+      <c r="T39" s="43"/>
+      <c r="U39" s="43"/>
+      <c r="V39" s="43"/>
+      <c r="W39" s="43"/>
+      <c r="X39" s="43"/>
+      <c r="Y39" s="42"/>
+      <c r="Z39" s="42"/>
+    </row>
+    <row r="40" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="42"/>
+      <c r="B40" s="42"/>
+      <c r="C40" s="42"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="42"/>
+      <c r="G40" s="42" t="s">
+        <v>120</v>
+      </c>
+      <c r="H40" s="42"/>
+      <c r="I40" s="42" t="s">
+        <v>52</v>
+      </c>
+      <c r="J40" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="K40" s="43"/>
+      <c r="L40" s="43">
+        <v>48</v>
+      </c>
+      <c r="M40" s="43">
+        <v>8</v>
+      </c>
+      <c r="N40" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="O40" s="43">
+        <v>0.1</v>
+      </c>
+      <c r="P40" s="43">
+        <v>-100.5</v>
+      </c>
+      <c r="Q40" s="43"/>
+      <c r="R40" s="43"/>
+      <c r="S40" s="43"/>
+      <c r="T40" s="43"/>
+      <c r="U40" s="43"/>
+      <c r="V40" s="43"/>
+      <c r="W40" s="43"/>
+      <c r="X40" s="43"/>
+      <c r="Y40" s="42"/>
+      <c r="Z40" s="42"/>
+    </row>
+    <row r="41" spans="1:26" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="42"/>
+      <c r="B41" s="42"/>
+      <c r="C41" s="42"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="42"/>
+      <c r="G41" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="H41" s="42"/>
+      <c r="I41" s="42" t="s">
+        <v>52</v>
+      </c>
+      <c r="J41" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="K41" s="43"/>
+      <c r="L41" s="43">
+        <v>56</v>
+      </c>
+      <c r="M41" s="43">
+        <v>8</v>
+      </c>
+      <c r="N41" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="O41" s="43">
+        <v>0.1</v>
+      </c>
+      <c r="P41" s="43">
+        <v>100</v>
+      </c>
+      <c r="Q41" s="43"/>
+      <c r="R41" s="43"/>
+      <c r="S41" s="43"/>
+      <c r="T41" s="43"/>
+      <c r="U41" s="43"/>
+      <c r="V41" s="43"/>
+      <c r="W41" s="43"/>
+      <c r="X41" s="43"/>
+      <c r="Y41" s="42"/>
+      <c r="Z41" s="42"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="44" type="noConversion"/>
   <dataValidations count="10">
@@ -9693,7 +11323,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{00000000-0002-0000-0300-000003000000}">
       <formula1>"Cycle,Event, IfActive,CE,CA"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576 K2:M1048576" xr:uid="{00000000-0002-0000-0300-000004000000}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:M1048576 E2:E1048576" xr:uid="{00000000-0002-0000-0300-000004000000}">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576" xr:uid="{00000000-0002-0000-0300-000005000000}">
@@ -9856,24 +11486,24 @@
         <v>39</v>
       </c>
       <c r="AG1" s="21" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="AH1" s="21" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2" spans="1:34" s="2" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B2" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>71</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>73</v>
       </c>
       <c r="E2" s="11">
         <v>100</v>
@@ -9908,10 +11538,10 @@
       <c r="AE2" s="10"/>
       <c r="AF2" s="10"/>
       <c r="AG2" s="10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AH2" s="10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -9922,7 +11552,7 @@
       <c r="E3" s="13"/>
       <c r="F3" s="12"/>
       <c r="G3" s="12" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
@@ -9968,7 +11598,7 @@
       <c r="E4" s="13"/>
       <c r="F4" s="12"/>
       <c r="G4" s="12" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
@@ -10008,16 +11638,16 @@
     </row>
     <row r="5" spans="1:34" s="2" customFormat="1" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>71</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>73</v>
       </c>
       <c r="E5" s="11">
         <v>100</v>
@@ -10052,10 +11682,10 @@
       <c r="AE5" s="10"/>
       <c r="AF5" s="10"/>
       <c r="AG5" s="10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AH5" s="10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -10066,7 +11696,7 @@
       <c r="E6" s="13"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
@@ -10112,7 +11742,7 @@
       <c r="E7" s="13"/>
       <c r="F7" s="12"/>
       <c r="G7" s="12" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
@@ -10152,16 +11782,16 @@
     </row>
     <row r="8" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B8" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="D8" s="15" t="s">
         <v>71</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>73</v>
       </c>
       <c r="E8" s="16">
         <v>500</v>
@@ -10196,10 +11826,10 @@
       <c r="AE8" s="15"/>
       <c r="AF8" s="19"/>
       <c r="AG8" s="22" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AH8" s="22" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:34" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -10210,7 +11840,7 @@
       <c r="E9" s="13"/>
       <c r="F9" s="12"/>
       <c r="G9" s="12" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
@@ -10256,7 +11886,7 @@
       <c r="E10" s="13"/>
       <c r="F10" s="12"/>
       <c r="G10" s="12" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>

--- a/src/test/resources/excel/DBC模版.xlsx
+++ b/src/test/resources/excel/DBC模版.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_USER\SLC\Code\IDEA_Project\smartGrid\src\test\resources\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C30762E6-B2C3-4FCC-B22B-C7FA1D25D5BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF0B05F-9FAD-4E92-8E76-3E8DEE04C2B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="21000" tabRatio="476" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21000" tabRatio="476" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CanProtocol_Info" sheetId="7" r:id="rId1"/>
-    <sheet name="DbcList" sheetId="6" r:id="rId2"/>
-    <sheet name="Example" sheetId="1" r:id="rId3"/>
-    <sheet name="CAN1" sheetId="2" r:id="rId4"/>
-    <sheet name="CAN2" sheetId="5" r:id="rId5"/>
+    <sheet name="AttributeDefinition" sheetId="8" r:id="rId2"/>
+    <sheet name="DbcList" sheetId="6" r:id="rId3"/>
+    <sheet name="Example" sheetId="1" r:id="rId4"/>
+    <sheet name="CAN1" sheetId="2" r:id="rId5"/>
+    <sheet name="CAN2" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,857 +40,138 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>作者</author>
-    <author>石李城</author>
+    <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{BD51F242-2B3E-40A2-A2F9-5104A8D5D822}">
       <text>
         <r>
           <rPr>
             <b/>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入报文名称。
-1、以字母或下划线开头，并且只可能进一步由26个字母、数字和下划线组成。
-2、长度最多为128个字符。为了与较旧的工具兼容，长度不得超过32个字符。
-3、报文名称中请不要使用换行符、空格等无效格式。
-4、请一定填写报文名称，报文名称不能为空。
-5、请不要填写重复的报文名称。
-6、信号逐行填写，报文信息只填写在属于该报文的信号的第一行。</t>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+你在这里定义好了你的自定义属性的名称后，你可以在你的表头中使用你的这个自定义属性。
+然后你就可以在对应的列里边填入你的值即可。</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{35ADE984-0FD7-4F44-B354-B6143E7DBEF2}">
       <text>
         <r>
           <rPr>
             <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入报文类型。
-报文类型只能为：Normal,NM,Diag,Extended,Standard   中的一个。
-Normal 类型包括 Extended 和 Standard  。
-并且现程序根据id自动判断扩展帧 Extended 和标准帧 Standard ，故不必特地填写扩展帧
-请一定填写报文类型，报文类型不能为空。</t>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+值类型固定是整形、浮点型、字符串、枚举类型和16进制数值，共5个类型。</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{32141E84-366B-411C-A66D-81AF5211331D}">
       <text>
         <r>
           <rPr>
             <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">请输入11位的报文ID。
-1、请确定报文ID为16进制正整数。
-2、报文ID可以带有"0x"标识，也可以不带“0x”。
-3、请一定填写报文ID，报文ID不能为空。报文ID不能重复。
-4、标准帧范围0x0~0x7FF; 扩展帧范围0x0~0x1FFF_FFFF，现改为范围0x7FF~0x1FFF_FFFF。
-5、注意: 标准帧0x211那么在DBC编码里它就是0x211的十进制表示。如果是扩展帧，0x211就会变成0x211+0x8000_0000然后再变成十进制存储。DBC编码由此来识别是扩展帧还是标准帧。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <strike/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>6、 如果协议中只填写了报文ID且小于0x7FF，那么DBC编码的时候可以识别成标准帧也可以识别成扩展帧，程序将无法正确识别。</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-7、现程序自动将范围0x0~0x7FF识别成标准帧。范围0x7FF~0x1FFF_FFFF，识别成扩展帧。</t>
+最大值和最小值只有当值类型是数值类型的时候有效，例如说整形、浮点型和16进制数值。
+字符串和枚举类型则不适用最大值最小值。</t>
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{DC1A8136-C1B6-43DA-8EF0-0DE3CA605544}">
       <text>
         <r>
           <rPr>
             <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入报文发送类型。
-报文发送类型只能为：Cycle,Event, IfActive,CE,CA    中的一个。
-请确定大小写与建议值保持一致。
-请一定填写报文发送类型，报文发送类型不能为空，事件型 Event 报文可以可以不写周期。
-Cycle:周期型，按照一定周期循环发送
-Event:事件型，触发事件后，仅发送一次
-IfActive:事件周期型，触发事件后，按照周期循环发送一定次数
-当信号所在报文的发送类型为"Cycle"时，信号发送类型只能为"Cycle"。
-报文发送类型为"Event"时，报文中至少有一个信号的发送类型为"Event"。
-报文发送类型为"IfActive"时，报文中至少有一个信号的发送类型为"IfActive"。
-报文发送类型为"CE"时，报文中至少有一个信号的发送类型为"Event"。
-报文发送类型为"CA"时，报文中至少有一个信号的发送类型为"IfActive"。</t>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+默认值在任何的值类型时都有效。</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000005000000}">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{99D438C2-2010-452B-8414-6DE3120E73F7}">
       <text>
         <r>
           <rPr>
             <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入报文周期时间。
-请确定报文周期时间为10进制正整数。
-当是事件型报文时，报文周期时间可以为空。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000006000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入报文长度。
-请确定报文长度为10进制正整数。
-报文长度最好不要超过8。
-请一定填写报文长度，报文长度不能为空。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入信号名称。
-信号名称只能为数字、下划线、字母，长度不能超过32个字符。
-信号名称中请不要使用换行符、空格等无效格式。
-请一定填写信号名称，信号名称不能为空。
-信号信息逐行填写。
-请不要填写重复的信号名称。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入信号描述。
-信号描述请不要使用","（英文逗号）和";"（英文分号）等无效格式。
-信号描述可以为空。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入信号排列格式。
-1、信号排列格式只能为： Intel,Motorola LSB,Motorola MSB     中的一种。
-2、请一定填写信号排列格式，信号排列格式不能为空，为空则默认为英特尔格式。
-3、英特尔格式,数据的最低位存放在矩阵的最低位。
-4、摩托罗拉格式,数据最低位存放在矩阵的高位。
-5、Motorola_MSB  ;该格式与 DBC 文件(即用txt打开)的格式保持一致 ，即信号的起始位是 数据最低位 ，在矩阵中的位置是 MSB
-6、Motorola_LSB   ;该格式与 CANdb++ 软件中的格式一致 ，即信号的起始位是 数据最高位 ，在矩阵中的位置是 LSB 
-7、例如：同样占据矩阵中01234567这8个bit的信号。
-Intel 格式的数据最低位是0，起始位是0；
-Motorola_MSB 格式，数据最低位是7，起始位则是7;
-Motorola LSB 格式，数据最低位还是7，但是起始位和 Intel 格式一样是 0 ;</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">请输入信号发送类型。
-信号发送类型只能为  Cycle,OnWrite,OnWriteWithRepetition,OnChange,OnChangeWithRepetition,IfActive,IfActiveWithRepetition    中的一种。
-请一定填写信号发送类型，信号发送类型不能为空。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>1、当信号所在报文的发送类型为"Cycle"时</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">，信号发送类型只能为"Cycle"。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>2、当信号所在报文的发送类型为"Event"时</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">，信号发送类型只能为"OnWrite"，"OnWriteWithRepetition"，"OnChange"，"OnChangeWithRepetition"中的一种。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>3、当信号所在报文的发送类型为"IfActive"时</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">，信号发送类型只能为"IfActive"，"IfActiveWithRepetition"中的一种。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>4、当信号所在报文的发送类型为"CE"时</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">，信号发送类型只能为"OnWrite"，"OnWriteWithRepetition"，"OnChange"，"OnChangeWithRepetition"中的一种。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>5、当信号所在报文的发送类型为"CA"时</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>，信号发送类型只能为"IfActive"，"IfActiveWithRepetition"中的一种。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000B000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>起始字节不是必填项，起始位才是必填项，请填写信号在8*8矩阵的哪一个bit起始。
-请输入信号起始字节。
-请一定填写信号起始字节。
-请确定信号起始字节为10进制正整数。
-请确定信号的起始字节与起始位保持一致。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000C000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="等线"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入信号起始位。
-请一定填写信号起始位，起始位不能为空。
-请确定信号起始位为10进制正整数。
-请确定报文中的信号不重复排列。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000D000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入信号长度。
-请一定填写信号长度，信号长度不能为空。
-请确认信号长度为10进制正整数。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>有符号 、无符号、双精度和单精度类型。
-请输入信号数据类型。
-信号数据类型只能为  Unsigned,Signed,IEEE float,IEEE Double,Boolean    中的一种。
-请一定填写信号数据类型，信号数据类型不能为空。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000F000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入信号精度。
-信号精度只能为数字、小数点、或者分数。
-信号精度中请不要使用换行符、空格等无效格式。
-请一定填写信号精度，信号精度不能为空。
-精度不可以为0，因为是除数，为0后将无意义。
-物理值(实际值)= 原始值(总线值/未处理值)*精度 +偏移量</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000010000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入信号偏移量。
-信号偏移量只能为数字、小数点、负号。
-信号偏移量中请不要使用换行符、空格等无效格式。
-请一定填写信号偏移量，信号偏移量不能为空。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000011000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="等线"/>
-            <charset val="134"/>
-          </rPr>
-          <t>程序会校验你填入的最小值、最大值和初始值。根据信号的长度，以及精度和偏移量计算。
-如果不填，程序会自动帮你计算并填入默认值</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000012000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <rFont val="等线"/>
-            <charset val="134"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">之后的总线值都不是必填项目，填了我也不会管(除非有错)，但是之前的物理最小值和物理最大值和初始值是必填。如果物理最小值、物理最大值和物理初始值你也不想填；可以，程序会默认给默认值赋值成最小值，同时根据长度、精度和偏移量自动计算最小最大值。
-总线值即原始值，未经过处理的值。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="等线"/>
-            <charset val="134"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>物理值(实际值)= 原始值(总线值/未处理值)*精度 +偏移量</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="V1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000013000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入总线初始值。
-请确定信号初始值为16进制正整数。
-请确定信号初始值在信号总线最小值和信号总线最大值之间。
-信号初始值可以带有"0x"标识。
-信号初始值可以为空。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="W1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000014000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入信号无效值。
-请确定信号无效值为16进制正整数。
-请确定信号无效值在信号总线最小值和信号总线最大值之间。
-信号无效值可以带有"0x"标识。
-信号无效值可以为空。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="X1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000015000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入信号单位。
-信号单位请不要使用","（英文逗号）和";"（英文分号）等无效格式。
-信号单位可以为空。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000016000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">信号值描述
-采用键值对的方式描述数据，一个键值对应一个数据，例如 key:value
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>1、如何填写键：</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">请确定信号值描述的值没有超过信号长度能表达的值范围。
-带有0x的数会被识别成16进制数，不带的会被识别成10进制数。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>2、如何分割键和值：</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">使用等号、中文冒号、英文冒号分隔键和值。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>3、如何分割多个键值对：</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">使用句号、中英文分号、或者回车换行符分割一组键值对。
-又或者使用引号把单个注释项引起来。（不推荐引号这种写法）
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>4、如何填写值：</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>值描述的内容中可以出现逗号和小数点，但是不可以使用中英文分号、中英文冒号、等号、中英文引号、句号或者回车换行符，否则可能无法识别。简单来讲就是用于分割的符号不可以出现在内容中。
-启用值描述，本程序在检查值描述规则的时候，不符合规则的值描述会被当成注释直接添加到注释中。
-例如：
-0=预留；1=关闭；  2  :   开启 
-1=关闭；就是一组键值对，"1"表示键 ，"关闭"表示值</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="11"/>
-            <rFont val="等线"/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Z1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000017000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>这一栏可以填入报文或者信号的备注。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AA1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000018000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入信号非使能值。
-请确定信号非使能值为16进制正整数。
-请确定信号非使能值在信号总线最小值和信号总线最大值之间。
-信号非使能值可以带有"0x"标识。
-信号非使能值可以为空。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AB1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000019000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="等线"/>
-            <charset val="134"/>
-          </rPr>
-          <t>网关需求报文。
-理论上，网关不会读取路由表中任何数据，如果网关需要读取其中某一些数据，就填写Yes，否则填写No，或者不填</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AC1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">分组类型，或者说分组模式、即多路复用。当你需要在一个报文矩阵中的同一个位置，塞入两个或以上的报文时，就需要采用多路复用，也就是分组功能。否则会出现报文id重复错误，或者出现报文重叠错误。
-请填入以下三种类型的数据：默认分组，分组标志位和组号。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>1、默认分组。</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-请填入 ：默认、默认分组、不分组、Default、DefaultGroup、single 或者你干脆直接空着不填(</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>推荐默认分组直接不填</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>)（注意：是叫你不填，并不不是让你填写0）。默认分组就表示最基本的状态，如果该帧报文全是默认分组，则只可以表示64bit的数据。如果该帧报文同时还存在其他分组报文，那么默认分组的报文会出现在所有的分组中，并且位置一致</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">。就是说，当不同分组的报文发过来的时候，默认分组的报文都存在。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">2、分组标志位。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">请填入：分组标志位、标志位、GroupFlag、Flag。即可被识别成标志位。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>一个报文只可以有一个分组标志位。</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-标志位用于储存并表示当前报文的组号。虽然有了分组，信号就可以在该帧同一个位置表示多个数据，但是一次只能发送一个分组的数据，只能同时激活一组数据(当然，默认分组会一直处于激活状态)。故标志位就是用于表示该组数据的组号。不同分组的报文发过来的时候，分组标志位也不同。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">3、组号。
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请填入：“组号：67(替换成你的组号)”，“Num：50(替换成你的组号)”,“32(或者你直接填写一个数字也是可以的)”。</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>推荐直接填写数字组号即可，只能填写大于等于0的整型数。</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-组号用于标注分组，实现在8*8矩阵的同一个位置放上好几个数据。当当前报文的分组标志位是67时，只激活组号67的报文，程序按照组号67的规则来解析，以此类推。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AD1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001B000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入报文发送的快速周期。
-请确定报文发送的快速周期为10进制正整数。
-报文发送的快速周期可以为空。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AE1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001C000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入报文快速发送的次数。
-请确定报文快速发送的次数为10进制正整数。
-报文快速发送的次数可以为空。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AF1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001D000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="18"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>请输入报文延时时间。
-请确定报文延时时间为10进制正整数。
-报文延时时间可以为空。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AG1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001E000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>如果是发送节点，在报文所在行、节点所在列对应的单元格输入"s"。
-如果是接收节点，在报文所在行、节点所在列对应的单元格输入"r"。
-请确定报文一定有发送节点。
-信号可以没有接受节点。
-节点名称，以字母或下划线开头，并且只可能进一步由26个字母、数字和下划线组成，长度不得超过32个字符。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001F000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <rFont val="等线"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Normal 类型包括 Extended 和 Standard  。
-并且现程序根据id自动判断扩展帧 Extended 和标准帧 Standard ，故不必特地填写扩展帧</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000020000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="36"/>
-            <rFont val="Microsoft YaHei UI"/>
-            <charset val="134"/>
-          </rPr>
-          <t>注释不可以写到这里</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
+ </t>
         </r>
       </text>
     </comment>
@@ -904,7 +186,7 @@
     <author>石李城</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -923,7 +205,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
@@ -940,7 +222,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
         <r>
           <rPr>
@@ -979,7 +261,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
       <text>
         <r>
           <rPr>
@@ -1003,7 +285,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
+    <comment ref="E1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000005000000}">
       <text>
         <r>
           <rPr>
@@ -1018,7 +300,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000006000000}">
+    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000006000000}">
       <text>
         <r>
           <rPr>
@@ -1034,7 +316,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
+    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
       <text>
         <r>
           <rPr>
@@ -1052,7 +334,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
       <text>
         <r>
           <rPr>
@@ -1067,7 +349,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000009000000}">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
       <text>
         <r>
           <rPr>
@@ -1090,7 +372,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000A000000}">
+    <comment ref="J1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -1194,7 +476,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000B000000}">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -1211,7 +493,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000C000000}">
+    <comment ref="L1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -1227,7 +509,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000D000000}">
+    <comment ref="M1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -1242,7 +524,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000E000000}">
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -1258,7 +540,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000F000000}">
+    <comment ref="O1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -1276,7 +558,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000010000000}">
+    <comment ref="P1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000010000000}">
       <text>
         <r>
           <rPr>
@@ -1292,7 +574,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000011000000}">
+    <comment ref="Q1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000011000000}">
       <text>
         <r>
           <rPr>
@@ -1306,7 +588,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000012000000}">
+    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000012000000}">
       <text>
         <r>
           <rPr>
@@ -1331,7 +613,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000013000000}">
+    <comment ref="V1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000013000000}">
       <text>
         <r>
           <rPr>
@@ -1348,7 +630,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000014000000}">
+    <comment ref="W1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000014000000}">
       <text>
         <r>
           <rPr>
@@ -1365,7 +647,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000015000000}">
+    <comment ref="X1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000015000000}">
       <text>
         <r>
           <rPr>
@@ -1380,7 +662,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000016000000}">
+    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000016000000}">
       <text>
         <r>
           <rPr>
@@ -1481,7 +763,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000017000000}">
+    <comment ref="Z1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000017000000}">
       <text>
         <r>
           <rPr>
@@ -1494,7 +776,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000018000000}">
+    <comment ref="AA1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000018000000}">
       <text>
         <r>
           <rPr>
@@ -1511,7 +793,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000019000000}">
+    <comment ref="AB1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000019000000}">
       <text>
         <r>
           <rPr>
@@ -1525,7 +807,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00001A000000}">
+    <comment ref="AC1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001A000000}">
       <text>
         <r>
           <rPr>
@@ -1657,7 +939,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00001B000000}">
+    <comment ref="AD1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001B000000}">
       <text>
         <r>
           <rPr>
@@ -1672,7 +954,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00001C000000}">
+    <comment ref="AE1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001C000000}">
       <text>
         <r>
           <rPr>
@@ -1687,7 +969,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00001D000000}">
+    <comment ref="AF1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001D000000}">
       <text>
         <r>
           <rPr>
@@ -1702,7 +984,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00001E000000}">
+    <comment ref="AG1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001E000000}">
       <text>
         <r>
           <rPr>
@@ -1719,7 +1001,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B11" authorId="1" shapeId="0" xr:uid="{24EEFAFB-6A0F-4942-BA1F-8B2C15165DF7}">
+    <comment ref="B2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-00001F000000}">
       <text>
         <r>
           <rPr>
@@ -1733,7 +1015,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A12" authorId="1" shapeId="0" xr:uid="{222AE9C2-F0E7-470E-81F0-83082A08FAD3}">
+    <comment ref="A3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000020000000}">
       <text>
         <r>
           <rPr>
@@ -1765,7 +1047,7 @@
     <author>石李城</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
           <rPr>
@@ -1784,7 +1066,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000002000000}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
@@ -1801,7 +1083,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000003000000}">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <r>
           <rPr>
@@ -1840,7 +1122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000004000000}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
         <r>
           <rPr>
@@ -1864,7 +1146,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000005000000}">
+    <comment ref="E1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
         <r>
           <rPr>
@@ -1879,7 +1161,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000006000000}">
+    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000006000000}">
       <text>
         <r>
           <rPr>
@@ -1895,7 +1177,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000007000000}">
+    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
       <text>
         <r>
           <rPr>
@@ -1913,7 +1195,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000008000000}">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
       <text>
         <r>
           <rPr>
@@ -1928,7 +1210,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000009000000}">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000009000000}">
       <text>
         <r>
           <rPr>
@@ -1951,6 +1233,867 @@
         </r>
       </text>
     </comment>
+    <comment ref="J1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000A000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">请输入信号发送类型。
+信号发送类型只能为  Cycle,OnWrite,OnWriteWithRepetition,OnChange,OnChangeWithRepetition,IfActive,IfActiveWithRepetition    中的一种。
+请一定填写信号发送类型，信号发送类型不能为空。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>1、当信号所在报文的发送类型为"Cycle"时</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">，信号发送类型只能为"Cycle"。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>2、当信号所在报文的发送类型为"Event"时</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">，信号发送类型只能为"OnWrite"，"OnWriteWithRepetition"，"OnChange"，"OnChangeWithRepetition"中的一种。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>3、当信号所在报文的发送类型为"IfActive"时</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">，信号发送类型只能为"IfActive"，"IfActiveWithRepetition"中的一种。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>4、当信号所在报文的发送类型为"CE"时</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">，信号发送类型只能为"OnWrite"，"OnWriteWithRepetition"，"OnChange"，"OnChangeWithRepetition"中的一种。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>5、当信号所在报文的发送类型为"CA"时</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>，信号发送类型只能为"IfActive"，"IfActiveWithRepetition"中的一种。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000B000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>起始字节不是必填项，起始位才是必填项，请填写信号在8*8矩阵的哪一个bit起始。
+请输入信号起始字节。
+请一定填写信号起始字节。
+请确定信号起始字节为10进制正整数。
+请确定信号的起始字节与起始位保持一致。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000C000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="等线"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入信号起始位。
+请一定填写信号起始位，起始位不能为空。
+请确定信号起始位为10进制正整数。
+请确定报文中的信号不重复排列。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000D000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入信号长度。
+请一定填写信号长度，信号长度不能为空。
+请确认信号长度为10进制正整数。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000E000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>有符号 、无符号、双精度和单精度类型。
+请输入信号数据类型。
+信号数据类型只能为  Unsigned,Signed,IEEE float,IEEE Double,Boolean    中的一种。
+请一定填写信号数据类型，信号数据类型不能为空。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000F000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入信号精度。
+信号精度只能为数字、小数点、或者分数。
+信号精度中请不要使用换行符、空格等无效格式。
+请一定填写信号精度，信号精度不能为空。
+精度不可以为0，因为是除数，为0后将无意义。
+物理值(实际值)= 原始值(总线值/未处理值)*精度 +偏移量</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000010000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入信号偏移量。
+信号偏移量只能为数字、小数点、负号。
+信号偏移量中请不要使用换行符、空格等无效格式。
+请一定填写信号偏移量，信号偏移量不能为空。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000011000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="等线"/>
+            <charset val="134"/>
+          </rPr>
+          <t>程序会校验你填入的最小值、最大值和初始值。根据信号的长度，以及精度和偏移量计算。
+如果不填，程序会自动帮你计算并填入默认值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000012000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <rFont val="等线"/>
+            <charset val="134"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">之后的总线值都不是必填项目，填了我也不会管(除非有错)，但是之前的物理最小值和物理最大值和初始值是必填。如果物理最小值、物理最大值和物理初始值你也不想填；可以，程序会默认给默认值赋值成最小值，同时根据长度、精度和偏移量自动计算最小最大值。
+总线值即原始值，未经过处理的值。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="等线"/>
+            <charset val="134"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>物理值(实际值)= 原始值(总线值/未处理值)*精度 +偏移量</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000013000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入总线初始值。
+请确定信号初始值为16进制正整数。
+请确定信号初始值在信号总线最小值和信号总线最大值之间。
+信号初始值可以带有"0x"标识。
+信号初始值可以为空。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000014000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入信号无效值。
+请确定信号无效值为16进制正整数。
+请确定信号无效值在信号总线最小值和信号总线最大值之间。
+信号无效值可以带有"0x"标识。
+信号无效值可以为空。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000015000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入信号单位。
+信号单位请不要使用","（英文逗号）和";"（英文分号）等无效格式。
+信号单位可以为空。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000016000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">信号值描述
+采用键值对的方式描述数据，一个键值对应一个数据，例如 key:value
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>1、如何填写键：</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">请确定信号值描述的值没有超过信号长度能表达的值范围。
+带有0x的数会被识别成16进制数，不带的会被识别成10进制数。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>2、如何分割键和值：</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">使用等号、中文冒号、英文冒号分隔键和值。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>3、如何分割多个键值对：</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">使用句号、中英文分号、或者回车换行符分割一组键值对。
+又或者使用引号把单个注释项引起来。（不推荐引号这种写法）
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>4、如何填写值：</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>值描述的内容中可以出现逗号和小数点，但是不可以使用中英文分号、中英文冒号、等号、中英文引号、句号或者回车换行符，否则可能无法识别。简单来讲就是用于分割的符号不可以出现在内容中。
+启用值描述，本程序在检查值描述规则的时候，不符合规则的值描述会被当成注释直接添加到注释中。
+例如：
+0=预留；1=关闭；  2  :   开启 
+1=关闭；就是一组键值对，"1"表示键 ，"关闭"表示值</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <rFont val="等线"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Z1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000017000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>这一栏可以填入报文或者信号的备注。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AA1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000018000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入信号非使能值。
+请确定信号非使能值为16进制正整数。
+请确定信号非使能值在信号总线最小值和信号总线最大值之间。
+信号非使能值可以带有"0x"标识。
+信号非使能值可以为空。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AB1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000019000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="等线"/>
+            <charset val="134"/>
+          </rPr>
+          <t>网关需求报文。
+理论上，网关不会读取路由表中任何数据，如果网关需要读取其中某一些数据，就填写Yes，否则填写No，或者不填</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AC1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00001A000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">分组类型，或者说分组模式、即多路复用。当你需要在一个报文矩阵中的同一个位置，塞入两个或以上的报文时，就需要采用多路复用，也就是分组功能。否则会出现报文id重复错误，或者出现报文重叠错误。
+请填入以下三种类型的数据：默认分组，分组标志位和组号。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>1、默认分组。</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+请填入 ：默认、默认分组、不分组、Default、DefaultGroup、single 或者你干脆直接空着不填(</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>推荐默认分组直接不填</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>)（注意：是叫你不填，并不不是让你填写0）。默认分组就表示最基本的状态，如果该帧报文全是默认分组，则只可以表示64bit的数据。如果该帧报文同时还存在其他分组报文，那么默认分组的报文会出现在所有的分组中，并且位置一致</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">。就是说，当不同分组的报文发过来的时候，默认分组的报文都存在。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">2、分组标志位。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">请填入：分组标志位、标志位、GroupFlag、Flag。即可被识别成标志位。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>一个报文只可以有一个分组标志位。</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+标志位用于储存并表示当前报文的组号。虽然有了分组，信号就可以在该帧同一个位置表示多个数据，但是一次只能发送一个分组的数据，只能同时激活一组数据(当然，默认分组会一直处于激活状态)。故标志位就是用于表示该组数据的组号。不同分组的报文发过来的时候，分组标志位也不同。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">3、组号。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请填入：“组号：67(替换成你的组号)”，“Num：50(替换成你的组号)”,“32(或者你直接填写一个数字也是可以的)”。</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>推荐直接填写数字组号即可，只能填写大于等于0的整型数。</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+组号用于标注分组，实现在8*8矩阵的同一个位置放上好几个数据。当当前报文的分组标志位是67时，只激活组号67的报文，程序按照组号67的规则来解析，以此类推。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AD1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00001B000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入报文发送的快速周期。
+请确定报文发送的快速周期为10进制正整数。
+报文发送的快速周期可以为空。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AE1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00001C000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入报文快速发送的次数。
+请确定报文快速发送的次数为10进制正整数。
+报文快速发送的次数可以为空。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AF1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00001D000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="18"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入报文延时时间。
+请确定报文延时时间为10进制正整数。
+报文延时时间可以为空。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AG1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-00001E000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>如果是发送节点，在报文所在行、节点所在列对应的单元格输入"s"。
+如果是接收节点，在报文所在行、节点所在列对应的单元格输入"r"。
+请确定报文一定有发送节点。
+信号可以没有接受节点。
+节点名称，以字母或下划线开头，并且只可能进一步由26个字母、数字和下划线组成，长度不得超过32个字符。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B11" authorId="1" shapeId="0" xr:uid="{24EEFAFB-6A0F-4942-BA1F-8B2C15165DF7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <rFont val="等线"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Normal 类型包括 Extended 和 Standard  。
+并且现程序根据id自动判断扩展帧 Extended 和标准帧 Standard ，故不必特地填写扩展帧</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="1" shapeId="0" xr:uid="{222AE9C2-F0E7-470E-81F0-83082A08FAD3}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="36"/>
+            <rFont val="Microsoft YaHei UI"/>
+            <charset val="134"/>
+          </rPr>
+          <t>注释不可以写到这里</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>作者</author>
+    <author>石李城</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="16"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入报文名称。
+1、以字母或下划线开头，并且只可能进一步由26个字母、数字和下划线组成。
+2、长度最多为128个字符。为了与较旧的工具兼容，长度不得超过32个字符。
+3、报文名称中请不要使用换行符、空格等无效格式。
+4、请一定填写报文名称，报文名称不能为空。
+5、请不要填写重复的报文名称。
+6、信号逐行填写，报文信息只填写在属于该报文的信号的第一行。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入报文类型。
+报文类型只能为：Normal,NM,Diag,Extended,Standard   中的一个。
+Normal 类型包括 Extended 和 Standard  。
+并且现程序根据id自动判断扩展帧 Extended 和标准帧 Standard ，故不必特地填写扩展帧
+请一定填写报文类型，报文类型不能为空。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">请输入11位的报文ID。
+1、请确定报文ID为16进制正整数。
+2、报文ID可以带有"0x"标识，也可以不带“0x”。
+3、请一定填写报文ID，报文ID不能为空。报文ID不能重复。
+4、标准帧范围0x0~0x7FF; 扩展帧范围0x0~0x1FFF_FFFF，现改为范围0x7FF~0x1FFF_FFFF。
+5、注意: 标准帧0x211那么在DBC编码里它就是0x211的十进制表示。如果是扩展帧，0x211就会变成0x211+0x8000_0000然后再变成十进制存储。DBC编码由此来识别是扩展帧还是标准帧。
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <strike/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>6、 如果协议中只填写了报文ID且小于0x7FF，那么DBC编码的时候可以识别成标准帧也可以识别成扩展帧，程序将无法正确识别。</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+7、现程序自动将范围0x0~0x7FF识别成标准帧。范围0x7FF~0x1FFF_FFFF，识别成扩展帧。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000004000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入报文发送类型。
+报文发送类型只能为：Cycle,Event, IfActive,CE,CA    中的一个。
+请确定大小写与建议值保持一致。
+请一定填写报文发送类型，报文发送类型不能为空，事件型 Event 报文可以可以不写周期。
+Cycle:周期型，按照一定周期循环发送
+Event:事件型，触发事件后，仅发送一次
+IfActive:事件周期型，触发事件后，按照周期循环发送一定次数
+当信号所在报文的发送类型为"Cycle"时，信号发送类型只能为"Cycle"。
+报文发送类型为"Event"时，报文中至少有一个信号的发送类型为"Event"。
+报文发送类型为"IfActive"时，报文中至少有一个信号的发送类型为"IfActive"。
+报文发送类型为"CE"时，报文中至少有一个信号的发送类型为"Event"。
+报文发送类型为"CA"时，报文中至少有一个信号的发送类型为"IfActive"。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000005000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入报文周期时间。
+请确定报文周期时间为10进制正整数。
+当是事件型报文时，报文周期时间可以为空。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000006000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入报文长度。
+请确定报文长度为10进制正整数。
+报文长度最好不要超过8。
+请一定填写报文长度，报文长度不能为空。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000007000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入信号名称。
+信号名称只能为数字、下划线、字母，长度不能超过32个字符。
+信号名称中请不要使用换行符、空格等无效格式。
+请一定填写信号名称，信号名称不能为空。
+信号信息逐行填写。
+请不要填写重复的信号名称。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000008000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入信号描述。
+信号描述请不要使用","（英文逗号）和";"（英文分号）等无效格式。
+信号描述可以为空。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000009000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="14"/>
+            <rFont val="微软雅黑"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请输入信号排列格式。
+1、信号排列格式只能为： Intel,Motorola LSB,Motorola MSB     中的一种。
+2、请一定填写信号排列格式，信号排列格式不能为空，为空则默认为英特尔格式。
+3、英特尔格式,数据的最低位存放在矩阵的最低位。
+4、摩托罗拉格式,数据最低位存放在矩阵的高位。
+5、Motorola_MSB  ;该格式与 DBC 文件(即用txt打开)的格式保持一致 ，即信号的起始位是 数据最低位 ，在矩阵中的位置是 MSB
+6、Motorola_LSB   ;该格式与 CANdb++ 软件中的格式一致 ，即信号的起始位是 数据最高位 ，在矩阵中的位置是 LSB 
+7、例如：同样占据矩阵中01234567这8个bit的信号。
+Intel 格式的数据最低位是0，起始位是0；
+Motorola_MSB 格式，数据最低位是7，起始位则是7;
+Motorola LSB 格式，数据最低位还是7，但是起始位和 Intel 格式一样是 0 ;</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="J1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000A000000}">
       <text>
         <r>
@@ -2585,7 +2728,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="232">
   <si>
     <t>测试协议</t>
   </si>
@@ -3274,6 +3417,74 @@
   </si>
   <si>
     <t>CCSToCabin2</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义属性名称</t>
+    <phoneticPr fontId="48" type="noConversion"/>
+  </si>
+  <si>
+    <t>GwUsedMsg</t>
+    <phoneticPr fontId="48" type="noConversion"/>
+  </si>
+  <si>
+    <t>GwUsedMsg
+网关需求报文(非必填)</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义属性描述</t>
+    <phoneticPr fontId="48" type="noConversion"/>
+  </si>
+  <si>
+    <t>网关需求报文</t>
+    <phoneticPr fontId="48" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enumeration</t>
+  </si>
+  <si>
+    <t>自定义属性作用域</t>
+    <phoneticPr fontId="48" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义属性值类型</t>
+    <phoneticPr fontId="48" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义属性最小值</t>
+    <phoneticPr fontId="48" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义属性最大值</t>
+    <phoneticPr fontId="48" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义属性默认值</t>
+    <phoneticPr fontId="48" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义属性枚举表</t>
+    <phoneticPr fontId="48" type="noConversion"/>
+  </si>
+  <si>
+    <t>SignalMinValueHex
+总线最小值（十六进制）(非必填)19</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>SignalMaxValueHex
+总线最大值（十六进制）（非必填）20</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>InitialValueHex
+总线初始值（十六进制）（必填）21</t>
+    <phoneticPr fontId="44" type="noConversion"/>
+  </si>
+  <si>
+    <t>InvalidValueHex
+总线无效值（十六进制）（非必填）22</t>
     <phoneticPr fontId="44" type="noConversion"/>
   </si>
 </sst>
@@ -3284,7 +3495,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$¥-804]#,##0.0000000000000;[$¥-804]\-#,##0.0000000000000"/>
   </numFmts>
-  <fonts count="48" x14ac:knownFonts="1">
+  <fonts count="52" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3598,6 +3809,36 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="20">
     <fill>
@@ -3715,7 +3956,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -3831,6 +4072,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -3932,7 +4188,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4061,6 +4317,11 @@
     <xf numFmtId="0" fontId="47" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="38">
     <cellStyle name="Standard_SL(Template)_PF2010_C71 CAN CMX V1.1_100817" xfId="3" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
@@ -4408,6 +4669,85 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73A3D3AA-9247-454A-9796-2078BC41A26D}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.375" customWidth="1"/>
+    <col min="2" max="2" width="14.75" customWidth="1"/>
+    <col min="3" max="3" width="23.25" customWidth="1"/>
+    <col min="4" max="4" width="19.375" customWidth="1"/>
+    <col min="5" max="5" width="16.375" customWidth="1"/>
+    <col min="6" max="6" width="17.875" customWidth="1"/>
+    <col min="7" max="7" width="17.125" customWidth="1"/>
+    <col min="8" max="8" width="16.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="55" t="s">
+        <v>216</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>219</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>222</v>
+      </c>
+      <c r="D1" s="55" t="s">
+        <v>223</v>
+      </c>
+      <c r="E1" s="55" t="s">
+        <v>224</v>
+      </c>
+      <c r="F1" s="55" t="s">
+        <v>225</v>
+      </c>
+      <c r="G1" s="55" t="s">
+        <v>226</v>
+      </c>
+      <c r="H1" s="55" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="55" t="s">
+        <v>217</v>
+      </c>
+      <c r="B2" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56" t="s">
+        <v>221</v>
+      </c>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="56"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="48" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{50F88472-F2AC-41AE-A38C-683DE1D8CB7E}">
+      <formula1>"Integer, Float, String, Enumeration, Hex "</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -4456,7 +4796,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AH95"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.149999999999999" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
@@ -9157,7 +9497,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AH41"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.149999999999999" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
@@ -9251,17 +9591,17 @@
       <c r="S1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="T1" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="V1" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="W1" s="8" t="s">
-        <v>30</v>
+      <c r="T1" s="54" t="s">
+        <v>228</v>
+      </c>
+      <c r="U1" s="54" t="s">
+        <v>229</v>
+      </c>
+      <c r="V1" s="54" t="s">
+        <v>230</v>
+      </c>
+      <c r="W1" s="54" t="s">
+        <v>231</v>
       </c>
       <c r="X1" s="8" t="s">
         <v>31</v>
@@ -9275,8 +9615,8 @@
       <c r="AA1" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="AB1" s="8" t="s">
-        <v>35</v>
+      <c r="AB1" s="54" t="s">
+        <v>218</v>
       </c>
       <c r="AC1" s="8" t="s">
         <v>36</v>
@@ -11351,7 +11691,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AH10"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="19.149999999999999" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.25"/>

--- a/src/test/resources/excel/DBC模版.xlsx
+++ b/src/test/resources/excel/DBC模版.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_USER\SLC\Code\IDEA_Project\smartGrid\src\test\resources\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF0B05F-9FAD-4E92-8E76-3E8DEE04C2B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09AB49AD-F0A0-4604-AEE7-597C3F442DD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="21000" tabRatio="476" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="21000" tabRatio="476" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CanProtocol_Info" sheetId="7" r:id="rId1"/>
@@ -4188,7 +4188,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4322,6 +4322,9 @@
     </xf>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="46" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="38">
     <cellStyle name="Standard_SL(Template)_PF2010_C71 CAN CMX V1.1_100817" xfId="3" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
@@ -10084,7 +10087,7 @@
       <c r="F11" s="31">
         <v>8</v>
       </c>
-      <c r="G11" s="32"/>
+      <c r="G11" s="57"/>
       <c r="H11" s="31"/>
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
